--- a/docs/files-completion-list/frontend-codebase-migration/ui-pages-pages-increment-codebase-2.xlsx
+++ b/docs/files-completion-list/frontend-codebase-migration/ui-pages-pages-increment-codebase-2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SaaS Project\trading-alerts-saas-public\docs\files-completion-list\frontend-codebase-migration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{365709AD-EECD-429A-889F-B370D2F7D09B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC6D713E-5D11-4641-9B7D-78FFE5F1CB8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2059" uniqueCount="2045">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2059" uniqueCount="2043">
   <si>
     <t>No.</t>
   </si>
@@ -3028,12 +3028,6 @@
   </si>
   <si>
     <t xml:space="preserve"> `/affiliate/verify` </t>
-  </si>
-  <si>
-    <t>https://trading-conversational-ai-ui-pages.vercel.app/affiliate/verify</t>
-  </si>
-  <si>
-    <t>D:\SaaS Project\trading-alerts-saas-public\seed-code\trading-conversational-ai-ui-pages-increment\app\affiliate\verify\page.tsx</t>
   </si>
   <si>
     <t>NL47Codebase 2</t>
@@ -6204,7 +6198,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6254,6 +6248,15 @@
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -6300,7 +6303,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6324,6 +6327,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -9871,62 +9875,62 @@
       <c r="C48" t="s">
         <v>989</v>
       </c>
-      <c r="D48" s="11" t="s">
+      <c r="D48" s="15" t="s">
+        <v>1156</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>1156</v>
+      </c>
+      <c r="F48" s="9" t="s">
         <v>990</v>
       </c>
-      <c r="E48" s="4" t="s">
+      <c r="G48" s="9" t="s">
         <v>991</v>
       </c>
-      <c r="F48" s="9" t="s">
+      <c r="H48" s="9" t="s">
         <v>992</v>
       </c>
-      <c r="G48" s="9" t="s">
+      <c r="I48" s="9" t="s">
         <v>993</v>
       </c>
-      <c r="H48" s="9" t="s">
+      <c r="J48" s="9" t="s">
         <v>994</v>
       </c>
-      <c r="I48" s="9" t="s">
+      <c r="K48" t="s">
         <v>995</v>
       </c>
-      <c r="J48" s="9" t="s">
+      <c r="L48" t="s">
         <v>996</v>
       </c>
-      <c r="K48" t="s">
+      <c r="M48" t="s">
         <v>997</v>
       </c>
-      <c r="L48" t="s">
+      <c r="N48" t="s">
         <v>998</v>
       </c>
-      <c r="M48" t="s">
+      <c r="O48" t="s">
         <v>999</v>
       </c>
-      <c r="N48" t="s">
+      <c r="P48" t="s">
         <v>1000</v>
       </c>
-      <c r="O48" t="s">
+      <c r="Q48" t="s">
         <v>1001</v>
       </c>
-      <c r="P48" t="s">
+      <c r="R48" t="s">
         <v>1002</v>
       </c>
-      <c r="Q48" t="s">
+      <c r="S48" t="s">
         <v>1003</v>
       </c>
-      <c r="R48" t="s">
+      <c r="T48" t="s">
         <v>1004</v>
       </c>
-      <c r="S48" t="s">
+      <c r="U48" t="s">
         <v>1005</v>
       </c>
-      <c r="T48" t="s">
+      <c r="V48" t="s">
         <v>1006</v>
-      </c>
-      <c r="U48" t="s">
-        <v>1007</v>
-      </c>
-      <c r="V48" t="s">
-        <v>1008</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.55000000000000004">
@@ -9934,67 +9938,67 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C49" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D49" s="11" t="s">
         <v>1009</v>
       </c>
-      <c r="C49" t="s">
+      <c r="E49" s="4" t="s">
         <v>1010</v>
       </c>
-      <c r="D49" s="11" t="s">
+      <c r="F49" s="9" t="s">
         <v>1011</v>
       </c>
-      <c r="E49" s="4" t="s">
+      <c r="G49" s="9" t="s">
         <v>1012</v>
       </c>
-      <c r="F49" s="9" t="s">
+      <c r="H49" s="9" t="s">
         <v>1013</v>
       </c>
-      <c r="G49" s="9" t="s">
+      <c r="I49" s="9" t="s">
         <v>1014</v>
       </c>
-      <c r="H49" s="9" t="s">
+      <c r="J49" s="9" t="s">
         <v>1015</v>
       </c>
-      <c r="I49" s="9" t="s">
+      <c r="K49" t="s">
         <v>1016</v>
       </c>
-      <c r="J49" s="9" t="s">
+      <c r="L49" t="s">
         <v>1017</v>
       </c>
-      <c r="K49" t="s">
+      <c r="M49" t="s">
         <v>1018</v>
       </c>
-      <c r="L49" t="s">
+      <c r="N49" t="s">
         <v>1019</v>
       </c>
-      <c r="M49" t="s">
+      <c r="O49" t="s">
         <v>1020</v>
       </c>
-      <c r="N49" t="s">
+      <c r="P49" t="s">
         <v>1021</v>
       </c>
-      <c r="O49" t="s">
+      <c r="Q49" t="s">
         <v>1022</v>
       </c>
-      <c r="P49" t="s">
+      <c r="R49" t="s">
         <v>1023</v>
       </c>
-      <c r="Q49" t="s">
+      <c r="S49" t="s">
         <v>1024</v>
       </c>
-      <c r="R49" t="s">
+      <c r="T49" t="s">
         <v>1025</v>
       </c>
-      <c r="S49" t="s">
+      <c r="U49" t="s">
         <v>1026</v>
       </c>
-      <c r="T49" t="s">
+      <c r="V49" t="s">
         <v>1027</v>
-      </c>
-      <c r="U49" t="s">
-        <v>1028</v>
-      </c>
-      <c r="V49" t="s">
-        <v>1029</v>
       </c>
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.55000000000000004">
@@ -10002,67 +10006,67 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C50" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D50" s="11" t="s">
         <v>1030</v>
       </c>
-      <c r="C50" t="s">
+      <c r="E50" s="4" t="s">
         <v>1031</v>
       </c>
-      <c r="D50" s="11" t="s">
+      <c r="F50" s="9" t="s">
         <v>1032</v>
       </c>
-      <c r="E50" s="4" t="s">
+      <c r="G50" s="9" t="s">
         <v>1033</v>
       </c>
-      <c r="F50" s="9" t="s">
+      <c r="H50" s="9" t="s">
         <v>1034</v>
       </c>
-      <c r="G50" s="9" t="s">
+      <c r="I50" s="9" t="s">
         <v>1035</v>
       </c>
-      <c r="H50" s="9" t="s">
+      <c r="J50" s="9" t="s">
         <v>1036</v>
       </c>
-      <c r="I50" s="9" t="s">
+      <c r="K50" t="s">
         <v>1037</v>
       </c>
-      <c r="J50" s="9" t="s">
+      <c r="L50" t="s">
         <v>1038</v>
       </c>
-      <c r="K50" t="s">
+      <c r="M50" t="s">
         <v>1039</v>
       </c>
-      <c r="L50" t="s">
+      <c r="N50" t="s">
         <v>1040</v>
       </c>
-      <c r="M50" t="s">
+      <c r="O50" t="s">
         <v>1041</v>
       </c>
-      <c r="N50" t="s">
+      <c r="P50" t="s">
         <v>1042</v>
       </c>
-      <c r="O50" t="s">
+      <c r="Q50" t="s">
         <v>1043</v>
       </c>
-      <c r="P50" t="s">
+      <c r="R50" t="s">
         <v>1044</v>
       </c>
-      <c r="Q50" t="s">
+      <c r="S50" t="s">
         <v>1045</v>
       </c>
-      <c r="R50" t="s">
+      <c r="T50" t="s">
         <v>1046</v>
       </c>
-      <c r="S50" t="s">
+      <c r="U50" t="s">
         <v>1047</v>
       </c>
-      <c r="T50" t="s">
+      <c r="V50" t="s">
         <v>1048</v>
-      </c>
-      <c r="U50" t="s">
-        <v>1049</v>
-      </c>
-      <c r="V50" t="s">
-        <v>1050</v>
       </c>
     </row>
     <row r="51" spans="1:22" x14ac:dyDescent="0.55000000000000004">
@@ -10070,67 +10074,67 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C51" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D51" s="11" t="s">
         <v>1051</v>
       </c>
-      <c r="C51" t="s">
+      <c r="E51" s="10" t="s">
         <v>1052</v>
       </c>
-      <c r="D51" s="11" t="s">
+      <c r="F51" s="9" t="s">
         <v>1053</v>
       </c>
-      <c r="E51" s="10" t="s">
+      <c r="G51" s="9" t="s">
         <v>1054</v>
       </c>
-      <c r="F51" s="9" t="s">
+      <c r="H51" s="9" t="s">
         <v>1055</v>
       </c>
-      <c r="G51" s="9" t="s">
+      <c r="I51" s="9" t="s">
         <v>1056</v>
       </c>
-      <c r="H51" s="9" t="s">
+      <c r="J51" s="9" t="s">
         <v>1057</v>
       </c>
-      <c r="I51" s="9" t="s">
+      <c r="K51" t="s">
         <v>1058</v>
       </c>
-      <c r="J51" s="9" t="s">
+      <c r="L51" t="s">
         <v>1059</v>
       </c>
-      <c r="K51" t="s">
+      <c r="M51" t="s">
         <v>1060</v>
       </c>
-      <c r="L51" t="s">
+      <c r="N51" t="s">
         <v>1061</v>
       </c>
-      <c r="M51" t="s">
+      <c r="O51" t="s">
         <v>1062</v>
       </c>
-      <c r="N51" t="s">
+      <c r="P51" t="s">
         <v>1063</v>
       </c>
-      <c r="O51" t="s">
+      <c r="Q51" t="s">
         <v>1064</v>
       </c>
-      <c r="P51" t="s">
+      <c r="R51" t="s">
         <v>1065</v>
       </c>
-      <c r="Q51" t="s">
+      <c r="S51" t="s">
         <v>1066</v>
       </c>
-      <c r="R51" t="s">
+      <c r="T51" t="s">
         <v>1067</v>
       </c>
-      <c r="S51" t="s">
+      <c r="U51" t="s">
         <v>1068</v>
       </c>
-      <c r="T51" t="s">
+      <c r="V51" t="s">
         <v>1069</v>
-      </c>
-      <c r="U51" t="s">
-        <v>1070</v>
-      </c>
-      <c r="V51" t="s">
-        <v>1071</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.55000000000000004">
@@ -10138,67 +10142,67 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C52" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D52" s="11" t="s">
         <v>1072</v>
       </c>
-      <c r="C52" t="s">
+      <c r="E52" s="10" t="s">
         <v>1073</v>
       </c>
-      <c r="D52" s="11" t="s">
+      <c r="F52" s="9" t="s">
         <v>1074</v>
       </c>
-      <c r="E52" s="10" t="s">
+      <c r="G52" s="9" t="s">
         <v>1075</v>
       </c>
-      <c r="F52" s="9" t="s">
+      <c r="H52" s="9" t="s">
         <v>1076</v>
       </c>
-      <c r="G52" s="9" t="s">
+      <c r="I52" s="9" t="s">
         <v>1077</v>
       </c>
-      <c r="H52" s="9" t="s">
+      <c r="J52" s="9" t="s">
         <v>1078</v>
       </c>
-      <c r="I52" s="9" t="s">
+      <c r="K52" t="s">
         <v>1079</v>
       </c>
-      <c r="J52" s="9" t="s">
+      <c r="L52" t="s">
         <v>1080</v>
       </c>
-      <c r="K52" t="s">
+      <c r="M52" t="s">
         <v>1081</v>
       </c>
-      <c r="L52" t="s">
+      <c r="N52" t="s">
         <v>1082</v>
       </c>
-      <c r="M52" t="s">
+      <c r="O52" t="s">
         <v>1083</v>
       </c>
-      <c r="N52" t="s">
+      <c r="P52" t="s">
         <v>1084</v>
       </c>
-      <c r="O52" t="s">
+      <c r="Q52" t="s">
         <v>1085</v>
       </c>
-      <c r="P52" t="s">
+      <c r="R52" t="s">
         <v>1086</v>
       </c>
-      <c r="Q52" t="s">
+      <c r="S52" t="s">
         <v>1087</v>
       </c>
-      <c r="R52" t="s">
+      <c r="T52" t="s">
         <v>1088</v>
       </c>
-      <c r="S52" t="s">
+      <c r="U52" t="s">
         <v>1089</v>
       </c>
-      <c r="T52" t="s">
+      <c r="V52" t="s">
         <v>1090</v>
-      </c>
-      <c r="U52" t="s">
-        <v>1091</v>
-      </c>
-      <c r="V52" t="s">
-        <v>1092</v>
       </c>
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.55000000000000004">
@@ -10206,67 +10210,67 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C53" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D53" s="11" t="s">
         <v>1093</v>
       </c>
-      <c r="C53" t="s">
+      <c r="E53" s="4" t="s">
         <v>1094</v>
       </c>
-      <c r="D53" s="11" t="s">
+      <c r="F53" s="9" t="s">
         <v>1095</v>
       </c>
-      <c r="E53" s="4" t="s">
+      <c r="G53" s="9" t="s">
         <v>1096</v>
       </c>
-      <c r="F53" s="9" t="s">
+      <c r="H53" s="9" t="s">
         <v>1097</v>
       </c>
-      <c r="G53" s="9" t="s">
+      <c r="I53" s="9" t="s">
         <v>1098</v>
       </c>
-      <c r="H53" s="9" t="s">
+      <c r="J53" s="9" t="s">
         <v>1099</v>
       </c>
-      <c r="I53" s="9" t="s">
+      <c r="K53" t="s">
         <v>1100</v>
       </c>
-      <c r="J53" s="9" t="s">
+      <c r="L53" t="s">
         <v>1101</v>
       </c>
-      <c r="K53" t="s">
+      <c r="M53" t="s">
         <v>1102</v>
       </c>
-      <c r="L53" t="s">
+      <c r="N53" t="s">
         <v>1103</v>
       </c>
-      <c r="M53" t="s">
+      <c r="O53" t="s">
         <v>1104</v>
       </c>
-      <c r="N53" t="s">
+      <c r="P53" t="s">
         <v>1105</v>
       </c>
-      <c r="O53" t="s">
+      <c r="Q53" t="s">
         <v>1106</v>
       </c>
-      <c r="P53" t="s">
+      <c r="R53" t="s">
         <v>1107</v>
       </c>
-      <c r="Q53" t="s">
+      <c r="S53" t="s">
         <v>1108</v>
       </c>
-      <c r="R53" t="s">
+      <c r="T53" t="s">
         <v>1109</v>
       </c>
-      <c r="S53" t="s">
+      <c r="U53" t="s">
         <v>1110</v>
       </c>
-      <c r="T53" t="s">
+      <c r="V53" t="s">
         <v>1111</v>
-      </c>
-      <c r="U53" t="s">
-        <v>1112</v>
-      </c>
-      <c r="V53" t="s">
-        <v>1113</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.55000000000000004">
@@ -10274,67 +10278,67 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C54" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D54" s="11" t="s">
         <v>1114</v>
       </c>
-      <c r="C54" t="s">
+      <c r="E54" s="4" t="s">
         <v>1115</v>
       </c>
-      <c r="D54" s="11" t="s">
+      <c r="F54" s="9" t="s">
         <v>1116</v>
       </c>
-      <c r="E54" s="4" t="s">
+      <c r="G54" s="9" t="s">
         <v>1117</v>
       </c>
-      <c r="F54" s="9" t="s">
+      <c r="H54" s="9" t="s">
         <v>1118</v>
       </c>
-      <c r="G54" s="9" t="s">
+      <c r="I54" s="9" t="s">
         <v>1119</v>
       </c>
-      <c r="H54" s="9" t="s">
+      <c r="J54" s="9" t="s">
         <v>1120</v>
       </c>
-      <c r="I54" s="9" t="s">
+      <c r="K54" t="s">
         <v>1121</v>
       </c>
-      <c r="J54" s="9" t="s">
+      <c r="L54" t="s">
         <v>1122</v>
       </c>
-      <c r="K54" t="s">
+      <c r="M54" t="s">
         <v>1123</v>
       </c>
-      <c r="L54" t="s">
+      <c r="N54" t="s">
         <v>1124</v>
       </c>
-      <c r="M54" t="s">
+      <c r="O54" t="s">
         <v>1125</v>
       </c>
-      <c r="N54" t="s">
+      <c r="P54" t="s">
         <v>1126</v>
       </c>
-      <c r="O54" t="s">
+      <c r="Q54" t="s">
         <v>1127</v>
       </c>
-      <c r="P54" t="s">
+      <c r="R54" t="s">
         <v>1128</v>
       </c>
-      <c r="Q54" t="s">
+      <c r="S54" t="s">
         <v>1129</v>
       </c>
-      <c r="R54" t="s">
+      <c r="T54" t="s">
         <v>1130</v>
       </c>
-      <c r="S54" t="s">
+      <c r="U54" t="s">
         <v>1131</v>
       </c>
-      <c r="T54" t="s">
+      <c r="V54" t="s">
         <v>1132</v>
-      </c>
-      <c r="U54" t="s">
-        <v>1133</v>
-      </c>
-      <c r="V54" t="s">
-        <v>1134</v>
       </c>
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.55000000000000004">
@@ -10342,67 +10346,67 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C55" t="s">
+        <v>1134</v>
+      </c>
+      <c r="D55" s="11" t="s">
         <v>1135</v>
       </c>
-      <c r="C55" t="s">
+      <c r="E55" s="4" t="s">
         <v>1136</v>
       </c>
-      <c r="D55" s="11" t="s">
+      <c r="F55" s="9" t="s">
         <v>1137</v>
       </c>
-      <c r="E55" s="4" t="s">
+      <c r="G55" s="9" t="s">
         <v>1138</v>
       </c>
-      <c r="F55" s="9" t="s">
+      <c r="H55" s="9" t="s">
         <v>1139</v>
       </c>
-      <c r="G55" s="9" t="s">
+      <c r="I55" s="9" t="s">
         <v>1140</v>
       </c>
-      <c r="H55" s="9" t="s">
+      <c r="J55" s="9" t="s">
         <v>1141</v>
       </c>
-      <c r="I55" s="9" t="s">
+      <c r="K55" t="s">
         <v>1142</v>
       </c>
-      <c r="J55" s="9" t="s">
+      <c r="L55" t="s">
         <v>1143</v>
       </c>
-      <c r="K55" t="s">
+      <c r="M55" t="s">
         <v>1144</v>
       </c>
-      <c r="L55" t="s">
+      <c r="N55" t="s">
         <v>1145</v>
       </c>
-      <c r="M55" t="s">
+      <c r="O55" t="s">
         <v>1146</v>
       </c>
-      <c r="N55" t="s">
+      <c r="P55" t="s">
         <v>1147</v>
       </c>
-      <c r="O55" t="s">
+      <c r="Q55" t="s">
         <v>1148</v>
       </c>
-      <c r="P55" t="s">
+      <c r="R55" t="s">
         <v>1149</v>
       </c>
-      <c r="Q55" t="s">
+      <c r="S55" t="s">
         <v>1150</v>
       </c>
-      <c r="R55" t="s">
+      <c r="T55" t="s">
         <v>1151</v>
       </c>
-      <c r="S55" t="s">
+      <c r="U55" t="s">
         <v>1152</v>
       </c>
-      <c r="T55" t="s">
+      <c r="V55" t="s">
         <v>1153</v>
-      </c>
-      <c r="U55" t="s">
-        <v>1154</v>
-      </c>
-      <c r="V55" t="s">
-        <v>1155</v>
       </c>
     </row>
     <row r="56" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
@@ -10410,67 +10414,67 @@
         <v>55</v>
       </c>
       <c r="B56" s="1" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>1155</v>
+      </c>
+      <c r="D56" s="6" t="s">
         <v>1156</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="E56" s="6" t="s">
+        <v>1156</v>
+      </c>
+      <c r="F56" s="9" t="s">
         <v>1157</v>
       </c>
-      <c r="D56" s="6" t="s">
+      <c r="G56" s="9" t="s">
         <v>1158</v>
       </c>
-      <c r="E56" s="6" t="s">
-        <v>1158</v>
-      </c>
-      <c r="F56" s="9" t="s">
+      <c r="H56" s="9" t="s">
         <v>1159</v>
       </c>
-      <c r="G56" s="9" t="s">
+      <c r="I56" s="9" t="s">
         <v>1160</v>
       </c>
-      <c r="H56" s="9" t="s">
+      <c r="J56" s="9" t="s">
         <v>1161</v>
       </c>
-      <c r="I56" s="9" t="s">
+      <c r="K56" t="s">
         <v>1162</v>
       </c>
-      <c r="J56" s="9" t="s">
+      <c r="L56" t="s">
         <v>1163</v>
       </c>
-      <c r="K56" t="s">
+      <c r="M56" t="s">
         <v>1164</v>
       </c>
-      <c r="L56" t="s">
+      <c r="N56" t="s">
         <v>1165</v>
       </c>
-      <c r="M56" t="s">
+      <c r="O56" t="s">
         <v>1166</v>
       </c>
-      <c r="N56" t="s">
+      <c r="P56" t="s">
         <v>1167</v>
       </c>
-      <c r="O56" t="s">
+      <c r="Q56" t="s">
         <v>1168</v>
       </c>
-      <c r="P56" t="s">
+      <c r="R56" t="s">
         <v>1169</v>
       </c>
-      <c r="Q56" t="s">
+      <c r="S56" t="s">
         <v>1170</v>
       </c>
-      <c r="R56" t="s">
+      <c r="T56" t="s">
         <v>1171</v>
       </c>
-      <c r="S56" t="s">
+      <c r="U56" t="s">
         <v>1172</v>
       </c>
-      <c r="T56" t="s">
+      <c r="V56" t="s">
         <v>1173</v>
-      </c>
-      <c r="U56" t="s">
-        <v>1174</v>
-      </c>
-      <c r="V56" t="s">
-        <v>1175</v>
       </c>
     </row>
     <row r="57" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
@@ -10478,67 +10482,67 @@
         <v>56</v>
       </c>
       <c r="B57" s="1" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>1155</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>1156</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>1156</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>1175</v>
+      </c>
+      <c r="G57" s="9" t="s">
         <v>1176</v>
       </c>
-      <c r="C57" s="1" t="s">
-        <v>1157</v>
-      </c>
-      <c r="D57" s="6" t="s">
-        <v>1158</v>
-      </c>
-      <c r="E57" s="6" t="s">
-        <v>1158</v>
-      </c>
-      <c r="F57" s="9" t="s">
+      <c r="H57" s="9" t="s">
         <v>1177</v>
       </c>
-      <c r="G57" s="9" t="s">
+      <c r="I57" s="9" t="s">
         <v>1178</v>
       </c>
-      <c r="H57" s="9" t="s">
+      <c r="J57" s="9" t="s">
         <v>1179</v>
       </c>
-      <c r="I57" s="9" t="s">
+      <c r="K57" t="s">
         <v>1180</v>
       </c>
-      <c r="J57" s="9" t="s">
+      <c r="L57" t="s">
         <v>1181</v>
       </c>
-      <c r="K57" t="s">
+      <c r="M57" t="s">
         <v>1182</v>
       </c>
-      <c r="L57" t="s">
+      <c r="N57" t="s">
         <v>1183</v>
       </c>
-      <c r="M57" t="s">
+      <c r="O57" t="s">
         <v>1184</v>
       </c>
-      <c r="N57" t="s">
+      <c r="P57" t="s">
         <v>1185</v>
       </c>
-      <c r="O57" t="s">
+      <c r="Q57" t="s">
         <v>1186</v>
       </c>
-      <c r="P57" t="s">
+      <c r="R57" t="s">
         <v>1187</v>
       </c>
-      <c r="Q57" t="s">
+      <c r="S57" t="s">
         <v>1188</v>
       </c>
-      <c r="R57" t="s">
+      <c r="T57" t="s">
         <v>1189</v>
       </c>
-      <c r="S57" t="s">
+      <c r="U57" t="s">
         <v>1190</v>
       </c>
-      <c r="T57" t="s">
+      <c r="V57" t="s">
         <v>1191</v>
-      </c>
-      <c r="U57" t="s">
-        <v>1192</v>
-      </c>
-      <c r="V57" t="s">
-        <v>1193</v>
       </c>
     </row>
     <row r="58" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
@@ -10546,67 +10550,67 @@
         <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="C58" s="1" t="s">
+        <v>1193</v>
+      </c>
+      <c r="D58" s="11" t="s">
         <v>1195</v>
       </c>
-      <c r="D58" s="11" t="s">
+      <c r="E58" s="6" t="s">
+        <v>1196</v>
+      </c>
+      <c r="F58" s="9" t="s">
         <v>1197</v>
       </c>
-      <c r="E58" s="6" t="s">
+      <c r="G58" s="9" t="s">
         <v>1198</v>
       </c>
-      <c r="F58" s="9" t="s">
+      <c r="H58" s="9" t="s">
         <v>1199</v>
       </c>
-      <c r="G58" s="9" t="s">
+      <c r="I58" s="9" t="s">
         <v>1200</v>
       </c>
-      <c r="H58" s="9" t="s">
+      <c r="J58" s="9" t="s">
         <v>1201</v>
       </c>
-      <c r="I58" s="9" t="s">
+      <c r="K58" t="s">
         <v>1202</v>
       </c>
-      <c r="J58" s="9" t="s">
+      <c r="L58" t="s">
         <v>1203</v>
       </c>
-      <c r="K58" t="s">
+      <c r="M58" t="s">
         <v>1204</v>
       </c>
-      <c r="L58" t="s">
+      <c r="N58" t="s">
         <v>1205</v>
       </c>
-      <c r="M58" t="s">
+      <c r="O58" t="s">
         <v>1206</v>
       </c>
-      <c r="N58" t="s">
+      <c r="P58" t="s">
         <v>1207</v>
       </c>
-      <c r="O58" t="s">
+      <c r="Q58" t="s">
         <v>1208</v>
       </c>
-      <c r="P58" t="s">
+      <c r="R58" t="s">
         <v>1209</v>
       </c>
-      <c r="Q58" t="s">
+      <c r="S58" t="s">
         <v>1210</v>
       </c>
-      <c r="R58" t="s">
+      <c r="T58" t="s">
         <v>1211</v>
       </c>
-      <c r="S58" t="s">
+      <c r="U58" t="s">
         <v>1212</v>
       </c>
-      <c r="T58" t="s">
+      <c r="V58" t="s">
         <v>1213</v>
-      </c>
-      <c r="U58" t="s">
-        <v>1214</v>
-      </c>
-      <c r="V58" t="s">
-        <v>1215</v>
       </c>
     </row>
     <row r="59" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
@@ -10614,67 +10618,67 @@
         <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>1215</v>
+      </c>
+      <c r="D59" s="11" t="s">
         <v>1216</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="E59" s="6" t="s">
         <v>1217</v>
       </c>
-      <c r="D59" s="11" t="s">
+      <c r="F59" s="9" t="s">
         <v>1218</v>
       </c>
-      <c r="E59" s="6" t="s">
+      <c r="G59" s="9" t="s">
         <v>1219</v>
       </c>
-      <c r="F59" s="9" t="s">
+      <c r="H59" s="9" t="s">
         <v>1220</v>
       </c>
-      <c r="G59" s="9" t="s">
+      <c r="I59" s="9" t="s">
         <v>1221</v>
       </c>
-      <c r="H59" s="9" t="s">
+      <c r="J59" s="9" t="s">
         <v>1222</v>
       </c>
-      <c r="I59" s="9" t="s">
+      <c r="K59" t="s">
         <v>1223</v>
       </c>
-      <c r="J59" s="9" t="s">
+      <c r="L59" t="s">
         <v>1224</v>
       </c>
-      <c r="K59" t="s">
+      <c r="M59" t="s">
         <v>1225</v>
       </c>
-      <c r="L59" t="s">
+      <c r="N59" t="s">
         <v>1226</v>
       </c>
-      <c r="M59" t="s">
+      <c r="O59" t="s">
         <v>1227</v>
       </c>
-      <c r="N59" t="s">
+      <c r="P59" t="s">
         <v>1228</v>
       </c>
-      <c r="O59" t="s">
+      <c r="Q59" t="s">
         <v>1229</v>
       </c>
-      <c r="P59" t="s">
+      <c r="R59" t="s">
         <v>1230</v>
       </c>
-      <c r="Q59" t="s">
+      <c r="S59" t="s">
         <v>1231</v>
       </c>
-      <c r="R59" t="s">
+      <c r="T59" t="s">
         <v>1232</v>
       </c>
-      <c r="S59" t="s">
+      <c r="U59" t="s">
         <v>1233</v>
       </c>
-      <c r="T59" t="s">
+      <c r="V59" t="s">
         <v>1234</v>
-      </c>
-      <c r="U59" t="s">
-        <v>1235</v>
-      </c>
-      <c r="V59" t="s">
-        <v>1236</v>
       </c>
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.55000000000000004">
@@ -10682,67 +10686,67 @@
         <v>59</v>
       </c>
       <c r="B60" s="1" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>1236</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>1156</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>1156</v>
+      </c>
+      <c r="F60" s="9" t="s">
         <v>1237</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="G60" s="9" t="s">
         <v>1238</v>
       </c>
-      <c r="D60" s="6" t="s">
-        <v>1158</v>
-      </c>
-      <c r="E60" s="6" t="s">
-        <v>1158</v>
-      </c>
-      <c r="F60" s="9" t="s">
+      <c r="H60" s="9" t="s">
         <v>1239</v>
       </c>
-      <c r="G60" s="9" t="s">
+      <c r="I60" s="9" t="s">
         <v>1240</v>
       </c>
-      <c r="H60" s="9" t="s">
+      <c r="J60" s="9" t="s">
         <v>1241</v>
       </c>
-      <c r="I60" s="9" t="s">
+      <c r="K60" t="s">
         <v>1242</v>
       </c>
-      <c r="J60" s="9" t="s">
+      <c r="L60" t="s">
         <v>1243</v>
       </c>
-      <c r="K60" t="s">
+      <c r="M60" t="s">
         <v>1244</v>
       </c>
-      <c r="L60" t="s">
+      <c r="N60" t="s">
         <v>1245</v>
       </c>
-      <c r="M60" t="s">
+      <c r="O60" t="s">
         <v>1246</v>
       </c>
-      <c r="N60" t="s">
+      <c r="P60" t="s">
         <v>1247</v>
       </c>
-      <c r="O60" t="s">
+      <c r="Q60" t="s">
         <v>1248</v>
       </c>
-      <c r="P60" t="s">
+      <c r="R60" t="s">
         <v>1249</v>
       </c>
-      <c r="Q60" t="s">
+      <c r="S60" t="s">
         <v>1250</v>
       </c>
-      <c r="R60" t="s">
+      <c r="T60" t="s">
         <v>1251</v>
       </c>
-      <c r="S60" t="s">
+      <c r="U60" t="s">
         <v>1252</v>
       </c>
-      <c r="T60" t="s">
+      <c r="V60" t="s">
         <v>1253</v>
-      </c>
-      <c r="U60" t="s">
-        <v>1254</v>
-      </c>
-      <c r="V60" t="s">
-        <v>1255</v>
       </c>
     </row>
     <row r="61" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
@@ -10750,67 +10754,67 @@
         <v>60</v>
       </c>
       <c r="B61" s="2" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D61" s="11" t="s">
         <v>1256</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="E61" s="7" t="s">
         <v>1257</v>
       </c>
-      <c r="D61" s="11" t="s">
+      <c r="F61" s="9" t="s">
         <v>1258</v>
       </c>
-      <c r="E61" s="7" t="s">
+      <c r="G61" s="9" t="s">
         <v>1259</v>
       </c>
-      <c r="F61" s="9" t="s">
+      <c r="H61" s="9" t="s">
         <v>1260</v>
       </c>
-      <c r="G61" s="9" t="s">
+      <c r="I61" s="9" t="s">
         <v>1261</v>
       </c>
-      <c r="H61" s="9" t="s">
+      <c r="J61" s="9" t="s">
         <v>1262</v>
       </c>
-      <c r="I61" s="9" t="s">
+      <c r="K61" t="s">
         <v>1263</v>
       </c>
-      <c r="J61" s="9" t="s">
+      <c r="L61" t="s">
         <v>1264</v>
       </c>
-      <c r="K61" t="s">
+      <c r="M61" t="s">
         <v>1265</v>
       </c>
-      <c r="L61" t="s">
+      <c r="N61" t="s">
         <v>1266</v>
       </c>
-      <c r="M61" t="s">
+      <c r="O61" t="s">
         <v>1267</v>
       </c>
-      <c r="N61" t="s">
+      <c r="P61" t="s">
         <v>1268</v>
       </c>
-      <c r="O61" t="s">
+      <c r="Q61" t="s">
         <v>1269</v>
       </c>
-      <c r="P61" t="s">
+      <c r="R61" t="s">
         <v>1270</v>
       </c>
-      <c r="Q61" t="s">
+      <c r="S61" t="s">
         <v>1271</v>
       </c>
-      <c r="R61" t="s">
+      <c r="T61" t="s">
         <v>1272</v>
       </c>
-      <c r="S61" t="s">
+      <c r="U61" t="s">
         <v>1273</v>
       </c>
-      <c r="T61" t="s">
+      <c r="V61" t="s">
         <v>1274</v>
-      </c>
-      <c r="U61" t="s">
-        <v>1275</v>
-      </c>
-      <c r="V61" t="s">
-        <v>1276</v>
       </c>
     </row>
     <row r="62" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
@@ -10818,67 +10822,67 @@
         <v>61</v>
       </c>
       <c r="B62" s="2" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>1276</v>
+      </c>
+      <c r="D62" s="11" t="s">
         <v>1277</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="E62" s="10" t="s">
         <v>1278</v>
       </c>
-      <c r="D62" s="11" t="s">
+      <c r="F62" s="9" t="s">
         <v>1279</v>
       </c>
-      <c r="E62" s="10" t="s">
+      <c r="G62" s="9" t="s">
         <v>1280</v>
       </c>
-      <c r="F62" s="9" t="s">
+      <c r="H62" s="9" t="s">
         <v>1281</v>
       </c>
-      <c r="G62" s="9" t="s">
+      <c r="I62" s="9" t="s">
         <v>1282</v>
       </c>
-      <c r="H62" s="9" t="s">
+      <c r="J62" s="9" t="s">
         <v>1283</v>
       </c>
-      <c r="I62" s="9" t="s">
+      <c r="K62" t="s">
         <v>1284</v>
       </c>
-      <c r="J62" s="9" t="s">
+      <c r="L62" t="s">
         <v>1285</v>
       </c>
-      <c r="K62" t="s">
+      <c r="M62" t="s">
         <v>1286</v>
       </c>
-      <c r="L62" t="s">
+      <c r="N62" t="s">
         <v>1287</v>
       </c>
-      <c r="M62" t="s">
+      <c r="O62" t="s">
         <v>1288</v>
       </c>
-      <c r="N62" t="s">
+      <c r="P62" t="s">
         <v>1289</v>
       </c>
-      <c r="O62" t="s">
+      <c r="Q62" t="s">
         <v>1290</v>
       </c>
-      <c r="P62" t="s">
+      <c r="R62" t="s">
         <v>1291</v>
       </c>
-      <c r="Q62" t="s">
+      <c r="S62" t="s">
         <v>1292</v>
       </c>
-      <c r="R62" t="s">
+      <c r="T62" t="s">
         <v>1293</v>
       </c>
-      <c r="S62" t="s">
+      <c r="U62" t="s">
         <v>1294</v>
       </c>
-      <c r="T62" t="s">
+      <c r="V62" t="s">
         <v>1295</v>
-      </c>
-      <c r="U62" t="s">
-        <v>1296</v>
-      </c>
-      <c r="V62" t="s">
-        <v>1297</v>
       </c>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.55000000000000004">
@@ -10886,67 +10890,67 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C63" t="s">
+        <v>1297</v>
+      </c>
+      <c r="D63" s="13" t="s">
         <v>1298</v>
       </c>
-      <c r="C63" t="s">
+      <c r="E63" s="6" t="s">
         <v>1299</v>
       </c>
-      <c r="D63" s="13" t="s">
+      <c r="F63" s="9" t="s">
         <v>1300</v>
       </c>
-      <c r="E63" s="6" t="s">
+      <c r="G63" s="9" t="s">
         <v>1301</v>
       </c>
-      <c r="F63" s="9" t="s">
+      <c r="H63" s="9" t="s">
         <v>1302</v>
       </c>
-      <c r="G63" s="9" t="s">
+      <c r="I63" s="9" t="s">
         <v>1303</v>
       </c>
-      <c r="H63" s="9" t="s">
+      <c r="J63" s="9" t="s">
         <v>1304</v>
       </c>
-      <c r="I63" s="9" t="s">
+      <c r="K63" t="s">
         <v>1305</v>
       </c>
-      <c r="J63" s="9" t="s">
+      <c r="L63" t="s">
         <v>1306</v>
       </c>
-      <c r="K63" t="s">
+      <c r="M63" t="s">
         <v>1307</v>
       </c>
-      <c r="L63" t="s">
+      <c r="N63" t="s">
         <v>1308</v>
       </c>
-      <c r="M63" t="s">
+      <c r="O63" t="s">
         <v>1309</v>
       </c>
-      <c r="N63" t="s">
+      <c r="P63" t="s">
         <v>1310</v>
       </c>
-      <c r="O63" t="s">
+      <c r="Q63" t="s">
         <v>1311</v>
       </c>
-      <c r="P63" t="s">
+      <c r="R63" t="s">
         <v>1312</v>
       </c>
-      <c r="Q63" t="s">
+      <c r="S63" t="s">
         <v>1313</v>
       </c>
-      <c r="R63" t="s">
+      <c r="T63" t="s">
         <v>1314</v>
       </c>
-      <c r="S63" t="s">
+      <c r="U63" t="s">
         <v>1315</v>
       </c>
-      <c r="T63" t="s">
+      <c r="V63" t="s">
         <v>1316</v>
-      </c>
-      <c r="U63" t="s">
-        <v>1317</v>
-      </c>
-      <c r="V63" t="s">
-        <v>1318</v>
       </c>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.55000000000000004">
@@ -10954,67 +10958,67 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C64" t="s">
+        <v>1318</v>
+      </c>
+      <c r="D64" s="11" t="s">
         <v>1319</v>
       </c>
-      <c r="C64" t="s">
+      <c r="E64" s="4" t="s">
         <v>1320</v>
       </c>
-      <c r="D64" s="11" t="s">
+      <c r="F64" s="9" t="s">
         <v>1321</v>
       </c>
-      <c r="E64" s="4" t="s">
+      <c r="G64" s="9" t="s">
         <v>1322</v>
       </c>
-      <c r="F64" s="9" t="s">
+      <c r="H64" s="9" t="s">
         <v>1323</v>
       </c>
-      <c r="G64" s="9" t="s">
+      <c r="I64" s="9" t="s">
         <v>1324</v>
       </c>
-      <c r="H64" s="9" t="s">
+      <c r="J64" s="9" t="s">
         <v>1325</v>
       </c>
-      <c r="I64" s="9" t="s">
+      <c r="K64" t="s">
         <v>1326</v>
       </c>
-      <c r="J64" s="9" t="s">
+      <c r="L64" t="s">
         <v>1327</v>
       </c>
-      <c r="K64" t="s">
+      <c r="M64" t="s">
         <v>1328</v>
       </c>
-      <c r="L64" t="s">
+      <c r="N64" t="s">
         <v>1329</v>
       </c>
-      <c r="M64" t="s">
+      <c r="O64" t="s">
         <v>1330</v>
       </c>
-      <c r="N64" t="s">
+      <c r="P64" t="s">
         <v>1331</v>
       </c>
-      <c r="O64" t="s">
+      <c r="Q64" t="s">
         <v>1332</v>
       </c>
-      <c r="P64" t="s">
+      <c r="R64" t="s">
         <v>1333</v>
       </c>
-      <c r="Q64" t="s">
+      <c r="S64" t="s">
         <v>1334</v>
       </c>
-      <c r="R64" t="s">
+      <c r="T64" t="s">
         <v>1335</v>
       </c>
-      <c r="S64" t="s">
+      <c r="U64" t="s">
         <v>1336</v>
       </c>
-      <c r="T64" t="s">
+      <c r="V64" t="s">
         <v>1337</v>
-      </c>
-      <c r="U64" t="s">
-        <v>1338</v>
-      </c>
-      <c r="V64" t="s">
-        <v>1339</v>
       </c>
     </row>
     <row r="65" spans="1:22" x14ac:dyDescent="0.55000000000000004">
@@ -11022,67 +11026,67 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
+        <v>1338</v>
+      </c>
+      <c r="C65" t="s">
+        <v>1339</v>
+      </c>
+      <c r="D65" s="11" t="s">
         <v>1340</v>
       </c>
-      <c r="C65" t="s">
+      <c r="E65" s="4" t="s">
         <v>1341</v>
       </c>
-      <c r="D65" s="11" t="s">
+      <c r="F65" s="9" t="s">
         <v>1342</v>
       </c>
-      <c r="E65" s="4" t="s">
+      <c r="G65" s="9" t="s">
         <v>1343</v>
       </c>
-      <c r="F65" s="9" t="s">
+      <c r="H65" s="9" t="s">
         <v>1344</v>
       </c>
-      <c r="G65" s="9" t="s">
+      <c r="I65" s="9" t="s">
         <v>1345</v>
       </c>
-      <c r="H65" s="9" t="s">
+      <c r="J65" s="9" t="s">
         <v>1346</v>
       </c>
-      <c r="I65" s="9" t="s">
+      <c r="K65" t="s">
         <v>1347</v>
       </c>
-      <c r="J65" s="9" t="s">
+      <c r="L65" t="s">
         <v>1348</v>
       </c>
-      <c r="K65" t="s">
+      <c r="M65" t="s">
         <v>1349</v>
       </c>
-      <c r="L65" t="s">
+      <c r="N65" t="s">
         <v>1350</v>
       </c>
-      <c r="M65" t="s">
+      <c r="O65" t="s">
         <v>1351</v>
       </c>
-      <c r="N65" t="s">
+      <c r="P65" t="s">
         <v>1352</v>
       </c>
-      <c r="O65" t="s">
+      <c r="Q65" t="s">
         <v>1353</v>
       </c>
-      <c r="P65" t="s">
+      <c r="R65" t="s">
         <v>1354</v>
       </c>
-      <c r="Q65" t="s">
+      <c r="S65" t="s">
         <v>1355</v>
       </c>
-      <c r="R65" t="s">
+      <c r="T65" t="s">
         <v>1356</v>
       </c>
-      <c r="S65" t="s">
+      <c r="U65" t="s">
         <v>1357</v>
       </c>
-      <c r="T65" t="s">
+      <c r="V65" t="s">
         <v>1358</v>
-      </c>
-      <c r="U65" t="s">
-        <v>1359</v>
-      </c>
-      <c r="V65" t="s">
-        <v>1360</v>
       </c>
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.55000000000000004">
@@ -11090,67 +11094,67 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C66" t="s">
+        <v>1360</v>
+      </c>
+      <c r="D66" s="11" t="s">
         <v>1361</v>
       </c>
-      <c r="C66" t="s">
+      <c r="E66" s="10" t="s">
         <v>1362</v>
       </c>
-      <c r="D66" s="11" t="s">
+      <c r="F66" s="9" t="s">
         <v>1363</v>
       </c>
-      <c r="E66" s="10" t="s">
+      <c r="G66" s="9" t="s">
         <v>1364</v>
       </c>
-      <c r="F66" s="9" t="s">
+      <c r="H66" s="9" t="s">
         <v>1365</v>
       </c>
-      <c r="G66" s="9" t="s">
+      <c r="I66" s="9" t="s">
         <v>1366</v>
       </c>
-      <c r="H66" s="9" t="s">
+      <c r="J66" s="9" t="s">
         <v>1367</v>
       </c>
-      <c r="I66" s="9" t="s">
+      <c r="K66" t="s">
         <v>1368</v>
       </c>
-      <c r="J66" s="9" t="s">
+      <c r="L66" t="s">
         <v>1369</v>
       </c>
-      <c r="K66" t="s">
+      <c r="M66" t="s">
         <v>1370</v>
       </c>
-      <c r="L66" t="s">
+      <c r="N66" t="s">
         <v>1371</v>
       </c>
-      <c r="M66" t="s">
+      <c r="O66" t="s">
         <v>1372</v>
       </c>
-      <c r="N66" t="s">
+      <c r="P66" t="s">
         <v>1373</v>
       </c>
-      <c r="O66" t="s">
+      <c r="Q66" t="s">
         <v>1374</v>
       </c>
-      <c r="P66" t="s">
+      <c r="R66" t="s">
         <v>1375</v>
       </c>
-      <c r="Q66" t="s">
+      <c r="S66" t="s">
         <v>1376</v>
       </c>
-      <c r="R66" t="s">
+      <c r="T66" t="s">
         <v>1377</v>
       </c>
-      <c r="S66" t="s">
+      <c r="U66" t="s">
         <v>1378</v>
       </c>
-      <c r="T66" t="s">
+      <c r="V66" t="s">
         <v>1379</v>
-      </c>
-      <c r="U66" t="s">
-        <v>1380</v>
-      </c>
-      <c r="V66" t="s">
-        <v>1381</v>
       </c>
     </row>
     <row r="67" spans="1:22" x14ac:dyDescent="0.55000000000000004">
@@ -11158,67 +11162,67 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C67" t="s">
+        <v>1381</v>
+      </c>
+      <c r="D67" s="11" t="s">
         <v>1382</v>
       </c>
-      <c r="C67" t="s">
+      <c r="E67" s="4" t="s">
         <v>1383</v>
       </c>
-      <c r="D67" s="11" t="s">
+      <c r="F67" s="9" t="s">
         <v>1384</v>
       </c>
-      <c r="E67" s="4" t="s">
+      <c r="G67" s="9" t="s">
         <v>1385</v>
       </c>
-      <c r="F67" s="9" t="s">
+      <c r="H67" s="9" t="s">
         <v>1386</v>
       </c>
-      <c r="G67" s="9" t="s">
+      <c r="I67" s="9" t="s">
         <v>1387</v>
       </c>
-      <c r="H67" s="9" t="s">
+      <c r="J67" s="9" t="s">
         <v>1388</v>
       </c>
-      <c r="I67" s="9" t="s">
+      <c r="K67" t="s">
         <v>1389</v>
       </c>
-      <c r="J67" s="9" t="s">
+      <c r="L67" t="s">
         <v>1390</v>
       </c>
-      <c r="K67" t="s">
+      <c r="M67" t="s">
         <v>1391</v>
       </c>
-      <c r="L67" t="s">
+      <c r="N67" t="s">
         <v>1392</v>
       </c>
-      <c r="M67" t="s">
+      <c r="O67" t="s">
         <v>1393</v>
       </c>
-      <c r="N67" t="s">
+      <c r="P67" t="s">
         <v>1394</v>
       </c>
-      <c r="O67" t="s">
+      <c r="Q67" t="s">
         <v>1395</v>
       </c>
-      <c r="P67" t="s">
+      <c r="R67" t="s">
         <v>1396</v>
       </c>
-      <c r="Q67" t="s">
+      <c r="S67" t="s">
         <v>1397</v>
       </c>
-      <c r="R67" t="s">
+      <c r="T67" t="s">
         <v>1398</v>
       </c>
-      <c r="S67" t="s">
+      <c r="U67" t="s">
         <v>1399</v>
       </c>
-      <c r="T67" t="s">
+      <c r="V67" t="s">
         <v>1400</v>
-      </c>
-      <c r="U67" t="s">
-        <v>1401</v>
-      </c>
-      <c r="V67" t="s">
-        <v>1402</v>
       </c>
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.55000000000000004">
@@ -11226,67 +11230,67 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
+        <v>1401</v>
+      </c>
+      <c r="C68" t="s">
+        <v>1402</v>
+      </c>
+      <c r="D68" s="11" t="s">
         <v>1403</v>
       </c>
-      <c r="C68" t="s">
+      <c r="E68" s="10" t="s">
         <v>1404</v>
       </c>
-      <c r="D68" s="11" t="s">
+      <c r="F68" s="9" t="s">
         <v>1405</v>
       </c>
-      <c r="E68" s="10" t="s">
+      <c r="G68" s="9" t="s">
         <v>1406</v>
       </c>
-      <c r="F68" s="9" t="s">
+      <c r="H68" s="9" t="s">
         <v>1407</v>
       </c>
-      <c r="G68" s="9" t="s">
+      <c r="I68" s="9" t="s">
         <v>1408</v>
       </c>
-      <c r="H68" s="9" t="s">
+      <c r="J68" s="9" t="s">
         <v>1409</v>
       </c>
-      <c r="I68" s="9" t="s">
+      <c r="K68" t="s">
         <v>1410</v>
       </c>
-      <c r="J68" s="9" t="s">
+      <c r="L68" t="s">
         <v>1411</v>
       </c>
-      <c r="K68" t="s">
+      <c r="M68" t="s">
         <v>1412</v>
       </c>
-      <c r="L68" t="s">
+      <c r="N68" t="s">
         <v>1413</v>
       </c>
-      <c r="M68" t="s">
+      <c r="O68" t="s">
         <v>1414</v>
       </c>
-      <c r="N68" t="s">
+      <c r="P68" t="s">
         <v>1415</v>
       </c>
-      <c r="O68" t="s">
+      <c r="Q68" t="s">
         <v>1416</v>
       </c>
-      <c r="P68" t="s">
+      <c r="R68" t="s">
         <v>1417</v>
       </c>
-      <c r="Q68" t="s">
+      <c r="S68" t="s">
         <v>1418</v>
       </c>
-      <c r="R68" t="s">
+      <c r="T68" t="s">
         <v>1419</v>
       </c>
-      <c r="S68" t="s">
+      <c r="U68" t="s">
         <v>1420</v>
       </c>
-      <c r="T68" t="s">
+      <c r="V68" t="s">
         <v>1421</v>
-      </c>
-      <c r="U68" t="s">
-        <v>1422</v>
-      </c>
-      <c r="V68" t="s">
-        <v>1423</v>
       </c>
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.55000000000000004">
@@ -11294,67 +11298,67 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
+        <v>1422</v>
+      </c>
+      <c r="C69" t="s">
+        <v>1423</v>
+      </c>
+      <c r="D69" s="13" t="s">
         <v>1424</v>
       </c>
-      <c r="C69" t="s">
+      <c r="E69" s="4" t="s">
         <v>1425</v>
       </c>
-      <c r="D69" s="13" t="s">
+      <c r="F69" s="9" t="s">
         <v>1426</v>
       </c>
-      <c r="E69" s="4" t="s">
+      <c r="G69" s="9" t="s">
         <v>1427</v>
       </c>
-      <c r="F69" s="9" t="s">
+      <c r="H69" s="9" t="s">
         <v>1428</v>
       </c>
-      <c r="G69" s="9" t="s">
+      <c r="I69" s="9" t="s">
         <v>1429</v>
       </c>
-      <c r="H69" s="9" t="s">
+      <c r="J69" s="9" t="s">
         <v>1430</v>
       </c>
-      <c r="I69" s="9" t="s">
+      <c r="K69" t="s">
         <v>1431</v>
       </c>
-      <c r="J69" s="9" t="s">
+      <c r="L69" t="s">
         <v>1432</v>
       </c>
-      <c r="K69" t="s">
+      <c r="M69" t="s">
         <v>1433</v>
       </c>
-      <c r="L69" t="s">
+      <c r="N69" t="s">
         <v>1434</v>
       </c>
-      <c r="M69" t="s">
+      <c r="O69" t="s">
         <v>1435</v>
       </c>
-      <c r="N69" t="s">
+      <c r="P69" t="s">
         <v>1436</v>
       </c>
-      <c r="O69" t="s">
+      <c r="Q69" t="s">
         <v>1437</v>
       </c>
-      <c r="P69" t="s">
+      <c r="R69" t="s">
         <v>1438</v>
       </c>
-      <c r="Q69" t="s">
+      <c r="S69" t="s">
         <v>1439</v>
       </c>
-      <c r="R69" t="s">
+      <c r="T69" t="s">
         <v>1440</v>
       </c>
-      <c r="S69" t="s">
+      <c r="U69" t="s">
         <v>1441</v>
       </c>
-      <c r="T69" t="s">
+      <c r="V69" t="s">
         <v>1442</v>
-      </c>
-      <c r="U69" t="s">
-        <v>1443</v>
-      </c>
-      <c r="V69" t="s">
-        <v>1444</v>
       </c>
     </row>
     <row r="70" spans="1:22" x14ac:dyDescent="0.55000000000000004">
@@ -11362,67 +11366,67 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
+        <v>1443</v>
+      </c>
+      <c r="C70" t="s">
+        <v>1444</v>
+      </c>
+      <c r="D70" s="11" t="s">
         <v>1445</v>
       </c>
-      <c r="C70" t="s">
+      <c r="E70" s="10" t="s">
         <v>1446</v>
       </c>
-      <c r="D70" s="11" t="s">
+      <c r="F70" s="9" t="s">
         <v>1447</v>
       </c>
-      <c r="E70" s="10" t="s">
+      <c r="G70" s="9" t="s">
         <v>1448</v>
       </c>
-      <c r="F70" s="9" t="s">
+      <c r="H70" s="9" t="s">
         <v>1449</v>
       </c>
-      <c r="G70" s="9" t="s">
+      <c r="I70" s="9" t="s">
         <v>1450</v>
       </c>
-      <c r="H70" s="9" t="s">
+      <c r="J70" s="9" t="s">
         <v>1451</v>
       </c>
-      <c r="I70" s="9" t="s">
+      <c r="K70" t="s">
         <v>1452</v>
       </c>
-      <c r="J70" s="9" t="s">
+      <c r="L70" t="s">
         <v>1453</v>
       </c>
-      <c r="K70" t="s">
+      <c r="M70" t="s">
         <v>1454</v>
       </c>
-      <c r="L70" t="s">
+      <c r="N70" t="s">
         <v>1455</v>
       </c>
-      <c r="M70" t="s">
+      <c r="O70" t="s">
         <v>1456</v>
       </c>
-      <c r="N70" t="s">
+      <c r="P70" t="s">
         <v>1457</v>
       </c>
-      <c r="O70" t="s">
+      <c r="Q70" t="s">
         <v>1458</v>
       </c>
-      <c r="P70" t="s">
+      <c r="R70" t="s">
         <v>1459</v>
       </c>
-      <c r="Q70" t="s">
+      <c r="S70" t="s">
         <v>1460</v>
       </c>
-      <c r="R70" t="s">
+      <c r="T70" t="s">
         <v>1461</v>
       </c>
-      <c r="S70" t="s">
+      <c r="U70" t="s">
         <v>1462</v>
       </c>
-      <c r="T70" t="s">
+      <c r="V70" t="s">
         <v>1463</v>
-      </c>
-      <c r="U70" t="s">
-        <v>1464</v>
-      </c>
-      <c r="V70" t="s">
-        <v>1465</v>
       </c>
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.55000000000000004">
@@ -11430,67 +11434,67 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C71" t="s">
+        <v>1465</v>
+      </c>
+      <c r="D71" s="11" t="s">
         <v>1466</v>
       </c>
-      <c r="C71" t="s">
+      <c r="E71" s="4" t="s">
         <v>1467</v>
       </c>
-      <c r="D71" s="11" t="s">
+      <c r="F71" s="9" t="s">
         <v>1468</v>
       </c>
-      <c r="E71" s="4" t="s">
+      <c r="G71" s="9" t="s">
         <v>1469</v>
       </c>
-      <c r="F71" s="9" t="s">
+      <c r="H71" s="9" t="s">
         <v>1470</v>
       </c>
-      <c r="G71" s="9" t="s">
+      <c r="I71" s="9" t="s">
         <v>1471</v>
       </c>
-      <c r="H71" s="9" t="s">
+      <c r="J71" s="9" t="s">
         <v>1472</v>
       </c>
-      <c r="I71" s="9" t="s">
+      <c r="K71" t="s">
         <v>1473</v>
       </c>
-      <c r="J71" s="9" t="s">
+      <c r="L71" t="s">
         <v>1474</v>
       </c>
-      <c r="K71" t="s">
+      <c r="M71" t="s">
         <v>1475</v>
       </c>
-      <c r="L71" t="s">
+      <c r="N71" t="s">
         <v>1476</v>
       </c>
-      <c r="M71" t="s">
+      <c r="O71" t="s">
         <v>1477</v>
       </c>
-      <c r="N71" t="s">
+      <c r="P71" t="s">
         <v>1478</v>
       </c>
-      <c r="O71" t="s">
+      <c r="Q71" t="s">
         <v>1479</v>
       </c>
-      <c r="P71" t="s">
+      <c r="R71" t="s">
         <v>1480</v>
       </c>
-      <c r="Q71" t="s">
+      <c r="S71" t="s">
         <v>1481</v>
       </c>
-      <c r="R71" t="s">
+      <c r="T71" t="s">
         <v>1482</v>
       </c>
-      <c r="S71" t="s">
+      <c r="U71" t="s">
         <v>1483</v>
       </c>
-      <c r="T71" t="s">
+      <c r="V71" t="s">
         <v>1484</v>
-      </c>
-      <c r="U71" t="s">
-        <v>1485</v>
-      </c>
-      <c r="V71" t="s">
-        <v>1486</v>
       </c>
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.55000000000000004">
@@ -11498,67 +11502,67 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
+        <v>1485</v>
+      </c>
+      <c r="C72" t="s">
+        <v>1486</v>
+      </c>
+      <c r="D72" s="13" t="s">
         <v>1487</v>
       </c>
-      <c r="C72" t="s">
+      <c r="E72" s="10" t="s">
         <v>1488</v>
       </c>
-      <c r="D72" s="13" t="s">
+      <c r="F72" s="9" t="s">
         <v>1489</v>
       </c>
-      <c r="E72" s="10" t="s">
+      <c r="G72" s="9" t="s">
         <v>1490</v>
       </c>
-      <c r="F72" s="9" t="s">
+      <c r="H72" s="9" t="s">
         <v>1491</v>
       </c>
-      <c r="G72" s="9" t="s">
+      <c r="I72" s="9" t="s">
         <v>1492</v>
       </c>
-      <c r="H72" s="9" t="s">
+      <c r="J72" s="9" t="s">
         <v>1493</v>
       </c>
-      <c r="I72" s="9" t="s">
+      <c r="K72" t="s">
         <v>1494</v>
       </c>
-      <c r="J72" s="9" t="s">
+      <c r="L72" t="s">
         <v>1495</v>
       </c>
-      <c r="K72" t="s">
+      <c r="M72" t="s">
         <v>1496</v>
       </c>
-      <c r="L72" t="s">
+      <c r="N72" t="s">
         <v>1497</v>
       </c>
-      <c r="M72" t="s">
+      <c r="O72" t="s">
         <v>1498</v>
       </c>
-      <c r="N72" t="s">
+      <c r="P72" t="s">
         <v>1499</v>
       </c>
-      <c r="O72" t="s">
+      <c r="Q72" t="s">
         <v>1500</v>
       </c>
-      <c r="P72" t="s">
+      <c r="R72" t="s">
         <v>1501</v>
       </c>
-      <c r="Q72" t="s">
+      <c r="S72" t="s">
         <v>1502</v>
       </c>
-      <c r="R72" t="s">
+      <c r="T72" t="s">
         <v>1503</v>
       </c>
-      <c r="S72" t="s">
+      <c r="U72" t="s">
         <v>1504</v>
       </c>
-      <c r="T72" t="s">
+      <c r="V72" t="s">
         <v>1505</v>
-      </c>
-      <c r="U72" t="s">
-        <v>1506</v>
-      </c>
-      <c r="V72" t="s">
-        <v>1507</v>
       </c>
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.55000000000000004">
@@ -11566,67 +11570,67 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C73" t="s">
+        <v>1507</v>
+      </c>
+      <c r="D73" s="11" t="s">
         <v>1508</v>
       </c>
-      <c r="C73" t="s">
+      <c r="E73" s="4" t="s">
         <v>1509</v>
       </c>
-      <c r="D73" s="11" t="s">
+      <c r="F73" s="9" t="s">
         <v>1510</v>
       </c>
-      <c r="E73" s="4" t="s">
+      <c r="G73" s="9" t="s">
         <v>1511</v>
       </c>
-      <c r="F73" s="9" t="s">
+      <c r="H73" s="9" t="s">
         <v>1512</v>
       </c>
-      <c r="G73" s="9" t="s">
+      <c r="I73" s="9" t="s">
         <v>1513</v>
       </c>
-      <c r="H73" s="9" t="s">
+      <c r="J73" s="9" t="s">
         <v>1514</v>
       </c>
-      <c r="I73" s="9" t="s">
+      <c r="K73" t="s">
         <v>1515</v>
       </c>
-      <c r="J73" s="9" t="s">
+      <c r="L73" t="s">
         <v>1516</v>
       </c>
-      <c r="K73" t="s">
+      <c r="M73" t="s">
         <v>1517</v>
       </c>
-      <c r="L73" t="s">
+      <c r="N73" t="s">
         <v>1518</v>
       </c>
-      <c r="M73" t="s">
+      <c r="O73" t="s">
         <v>1519</v>
       </c>
-      <c r="N73" t="s">
+      <c r="P73" t="s">
         <v>1520</v>
       </c>
-      <c r="O73" t="s">
+      <c r="Q73" t="s">
         <v>1521</v>
       </c>
-      <c r="P73" t="s">
+      <c r="R73" t="s">
         <v>1522</v>
       </c>
-      <c r="Q73" t="s">
+      <c r="S73" t="s">
         <v>1523</v>
       </c>
-      <c r="R73" t="s">
+      <c r="T73" t="s">
         <v>1524</v>
       </c>
-      <c r="S73" t="s">
+      <c r="U73" t="s">
         <v>1525</v>
       </c>
-      <c r="T73" t="s">
+      <c r="V73" t="s">
         <v>1526</v>
-      </c>
-      <c r="U73" t="s">
-        <v>1527</v>
-      </c>
-      <c r="V73" t="s">
-        <v>1528</v>
       </c>
     </row>
     <row r="74" spans="1:22" x14ac:dyDescent="0.55000000000000004">
@@ -11634,67 +11638,67 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
+        <v>1527</v>
+      </c>
+      <c r="C74" t="s">
+        <v>1528</v>
+      </c>
+      <c r="D74" s="11" t="s">
         <v>1529</v>
       </c>
-      <c r="C74" t="s">
+      <c r="E74" s="10" t="s">
         <v>1530</v>
       </c>
-      <c r="D74" s="11" t="s">
+      <c r="F74" s="9" t="s">
         <v>1531</v>
       </c>
-      <c r="E74" s="10" t="s">
+      <c r="G74" s="9" t="s">
         <v>1532</v>
       </c>
-      <c r="F74" s="9" t="s">
+      <c r="H74" s="9" t="s">
         <v>1533</v>
       </c>
-      <c r="G74" s="9" t="s">
+      <c r="I74" s="9" t="s">
         <v>1534</v>
       </c>
-      <c r="H74" s="9" t="s">
+      <c r="J74" s="9" t="s">
         <v>1535</v>
       </c>
-      <c r="I74" s="9" t="s">
+      <c r="K74" t="s">
         <v>1536</v>
       </c>
-      <c r="J74" s="9" t="s">
+      <c r="L74" t="s">
         <v>1537</v>
       </c>
-      <c r="K74" t="s">
+      <c r="M74" t="s">
         <v>1538</v>
       </c>
-      <c r="L74" t="s">
+      <c r="N74" t="s">
         <v>1539</v>
       </c>
-      <c r="M74" t="s">
+      <c r="O74" t="s">
         <v>1540</v>
       </c>
-      <c r="N74" t="s">
+      <c r="P74" t="s">
         <v>1541</v>
       </c>
-      <c r="O74" t="s">
+      <c r="Q74" t="s">
         <v>1542</v>
       </c>
-      <c r="P74" t="s">
+      <c r="R74" t="s">
         <v>1543</v>
       </c>
-      <c r="Q74" t="s">
+      <c r="S74" t="s">
         <v>1544</v>
       </c>
-      <c r="R74" t="s">
+      <c r="T74" t="s">
         <v>1545</v>
       </c>
-      <c r="S74" t="s">
+      <c r="U74" t="s">
         <v>1546</v>
       </c>
-      <c r="T74" t="s">
+      <c r="V74" t="s">
         <v>1547</v>
-      </c>
-      <c r="U74" t="s">
-        <v>1548</v>
-      </c>
-      <c r="V74" t="s">
-        <v>1549</v>
       </c>
     </row>
     <row r="75" spans="1:22" x14ac:dyDescent="0.55000000000000004">
@@ -11702,67 +11706,67 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
+        <v>1548</v>
+      </c>
+      <c r="C75" t="s">
+        <v>1549</v>
+      </c>
+      <c r="D75" s="11" t="s">
         <v>1550</v>
       </c>
-      <c r="C75" t="s">
+      <c r="E75" s="6" t="s">
         <v>1551</v>
       </c>
-      <c r="D75" s="11" t="s">
+      <c r="F75" s="9" t="s">
         <v>1552</v>
       </c>
-      <c r="E75" s="6" t="s">
+      <c r="G75" s="9" t="s">
         <v>1553</v>
       </c>
-      <c r="F75" s="9" t="s">
+      <c r="H75" s="9" t="s">
         <v>1554</v>
       </c>
-      <c r="G75" s="9" t="s">
+      <c r="I75" s="9" t="s">
         <v>1555</v>
       </c>
-      <c r="H75" s="9" t="s">
+      <c r="J75" s="9" t="s">
         <v>1556</v>
       </c>
-      <c r="I75" s="9" t="s">
+      <c r="K75" t="s">
         <v>1557</v>
       </c>
-      <c r="J75" s="9" t="s">
+      <c r="L75" t="s">
         <v>1558</v>
       </c>
-      <c r="K75" t="s">
+      <c r="M75" t="s">
         <v>1559</v>
       </c>
-      <c r="L75" t="s">
+      <c r="N75" t="s">
         <v>1560</v>
       </c>
-      <c r="M75" t="s">
+      <c r="O75" t="s">
         <v>1561</v>
       </c>
-      <c r="N75" t="s">
+      <c r="P75" t="s">
         <v>1562</v>
       </c>
-      <c r="O75" t="s">
+      <c r="Q75" t="s">
         <v>1563</v>
       </c>
-      <c r="P75" t="s">
+      <c r="R75" t="s">
         <v>1564</v>
       </c>
-      <c r="Q75" t="s">
+      <c r="S75" t="s">
         <v>1565</v>
       </c>
-      <c r="R75" t="s">
+      <c r="T75" t="s">
         <v>1566</v>
       </c>
-      <c r="S75" t="s">
+      <c r="U75" t="s">
         <v>1567</v>
       </c>
-      <c r="T75" t="s">
+      <c r="V75" t="s">
         <v>1568</v>
-      </c>
-      <c r="U75" t="s">
-        <v>1569</v>
-      </c>
-      <c r="V75" t="s">
-        <v>1570</v>
       </c>
     </row>
     <row r="76" spans="1:22" x14ac:dyDescent="0.55000000000000004">
@@ -11770,67 +11774,67 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C76" t="s">
+        <v>1570</v>
+      </c>
+      <c r="D76" s="11" t="s">
         <v>1571</v>
       </c>
-      <c r="C76" t="s">
+      <c r="E76" s="10" t="s">
         <v>1572</v>
       </c>
-      <c r="D76" s="11" t="s">
+      <c r="F76" s="9" t="s">
         <v>1573</v>
       </c>
-      <c r="E76" s="10" t="s">
+      <c r="G76" s="9" t="s">
         <v>1574</v>
       </c>
-      <c r="F76" s="9" t="s">
+      <c r="H76" s="9" t="s">
         <v>1575</v>
       </c>
-      <c r="G76" s="9" t="s">
+      <c r="I76" s="9" t="s">
         <v>1576</v>
       </c>
-      <c r="H76" s="9" t="s">
+      <c r="J76" s="9" t="s">
         <v>1577</v>
       </c>
-      <c r="I76" s="9" t="s">
+      <c r="K76" t="s">
         <v>1578</v>
       </c>
-      <c r="J76" s="9" t="s">
+      <c r="L76" t="s">
         <v>1579</v>
       </c>
-      <c r="K76" t="s">
+      <c r="M76" t="s">
         <v>1580</v>
       </c>
-      <c r="L76" t="s">
+      <c r="N76" t="s">
         <v>1581</v>
       </c>
-      <c r="M76" t="s">
+      <c r="O76" t="s">
         <v>1582</v>
       </c>
-      <c r="N76" t="s">
+      <c r="P76" t="s">
         <v>1583</v>
       </c>
-      <c r="O76" t="s">
+      <c r="Q76" t="s">
         <v>1584</v>
       </c>
-      <c r="P76" t="s">
+      <c r="R76" t="s">
         <v>1585</v>
       </c>
-      <c r="Q76" t="s">
+      <c r="S76" t="s">
         <v>1586</v>
       </c>
-      <c r="R76" t="s">
+      <c r="T76" t="s">
         <v>1587</v>
       </c>
-      <c r="S76" t="s">
+      <c r="U76" t="s">
         <v>1588</v>
       </c>
-      <c r="T76" t="s">
+      <c r="V76" t="s">
         <v>1589</v>
-      </c>
-      <c r="U76" t="s">
-        <v>1590</v>
-      </c>
-      <c r="V76" t="s">
-        <v>1591</v>
       </c>
     </row>
     <row r="77" spans="1:22" x14ac:dyDescent="0.55000000000000004">
@@ -11838,67 +11842,67 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
+        <v>1590</v>
+      </c>
+      <c r="C77" t="s">
+        <v>1591</v>
+      </c>
+      <c r="D77" s="11" t="s">
         <v>1592</v>
       </c>
-      <c r="C77" t="s">
+      <c r="E77" s="6" t="s">
         <v>1593</v>
       </c>
-      <c r="D77" s="11" t="s">
+      <c r="F77" s="9" t="s">
         <v>1594</v>
       </c>
-      <c r="E77" s="6" t="s">
+      <c r="G77" s="9" t="s">
         <v>1595</v>
       </c>
-      <c r="F77" s="9" t="s">
+      <c r="H77" s="9" t="s">
         <v>1596</v>
       </c>
-      <c r="G77" s="9" t="s">
+      <c r="I77" s="9" t="s">
         <v>1597</v>
       </c>
-      <c r="H77" s="9" t="s">
+      <c r="J77" s="9" t="s">
         <v>1598</v>
       </c>
-      <c r="I77" s="9" t="s">
+      <c r="K77" t="s">
         <v>1599</v>
       </c>
-      <c r="J77" s="9" t="s">
+      <c r="L77" t="s">
         <v>1600</v>
       </c>
-      <c r="K77" t="s">
+      <c r="M77" t="s">
         <v>1601</v>
       </c>
-      <c r="L77" t="s">
+      <c r="N77" t="s">
         <v>1602</v>
       </c>
-      <c r="M77" t="s">
+      <c r="O77" t="s">
         <v>1603</v>
       </c>
-      <c r="N77" t="s">
+      <c r="P77" t="s">
         <v>1604</v>
       </c>
-      <c r="O77" t="s">
+      <c r="Q77" t="s">
         <v>1605</v>
       </c>
-      <c r="P77" t="s">
+      <c r="R77" t="s">
         <v>1606</v>
       </c>
-      <c r="Q77" t="s">
+      <c r="S77" t="s">
         <v>1607</v>
       </c>
-      <c r="R77" t="s">
+      <c r="T77" t="s">
         <v>1608</v>
       </c>
-      <c r="S77" t="s">
+      <c r="U77" t="s">
         <v>1609</v>
       </c>
-      <c r="T77" t="s">
+      <c r="V77" t="s">
         <v>1610</v>
-      </c>
-      <c r="U77" t="s">
-        <v>1611</v>
-      </c>
-      <c r="V77" t="s">
-        <v>1612</v>
       </c>
     </row>
     <row r="78" spans="1:22" x14ac:dyDescent="0.55000000000000004">
@@ -11906,67 +11910,67 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
+        <v>1611</v>
+      </c>
+      <c r="C78" t="s">
+        <v>1612</v>
+      </c>
+      <c r="D78" s="11" t="s">
         <v>1613</v>
       </c>
-      <c r="C78" t="s">
+      <c r="E78" s="10" t="s">
         <v>1614</v>
       </c>
-      <c r="D78" s="11" t="s">
+      <c r="F78" s="9" t="s">
         <v>1615</v>
       </c>
-      <c r="E78" s="10" t="s">
+      <c r="G78" s="9" t="s">
         <v>1616</v>
       </c>
-      <c r="F78" s="9" t="s">
+      <c r="H78" s="9" t="s">
         <v>1617</v>
       </c>
-      <c r="G78" s="9" t="s">
+      <c r="I78" s="9" t="s">
         <v>1618</v>
       </c>
-      <c r="H78" s="9" t="s">
+      <c r="J78" s="9" t="s">
         <v>1619</v>
       </c>
-      <c r="I78" s="9" t="s">
+      <c r="K78" t="s">
         <v>1620</v>
       </c>
-      <c r="J78" s="9" t="s">
+      <c r="L78" t="s">
         <v>1621</v>
       </c>
-      <c r="K78" t="s">
+      <c r="M78" t="s">
         <v>1622</v>
       </c>
-      <c r="L78" t="s">
+      <c r="N78" t="s">
         <v>1623</v>
       </c>
-      <c r="M78" t="s">
+      <c r="O78" t="s">
         <v>1624</v>
       </c>
-      <c r="N78" t="s">
+      <c r="P78" t="s">
         <v>1625</v>
       </c>
-      <c r="O78" t="s">
+      <c r="Q78" t="s">
         <v>1626</v>
       </c>
-      <c r="P78" t="s">
+      <c r="R78" t="s">
         <v>1627</v>
       </c>
-      <c r="Q78" t="s">
+      <c r="S78" t="s">
         <v>1628</v>
       </c>
-      <c r="R78" t="s">
+      <c r="T78" t="s">
         <v>1629</v>
       </c>
-      <c r="S78" t="s">
+      <c r="U78" t="s">
         <v>1630</v>
       </c>
-      <c r="T78" t="s">
+      <c r="V78" t="s">
         <v>1631</v>
-      </c>
-      <c r="U78" t="s">
-        <v>1632</v>
-      </c>
-      <c r="V78" t="s">
-        <v>1633</v>
       </c>
     </row>
     <row r="79" spans="1:22" x14ac:dyDescent="0.55000000000000004">
@@ -11974,67 +11978,67 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
+        <v>1632</v>
+      </c>
+      <c r="C79" t="s">
+        <v>1633</v>
+      </c>
+      <c r="D79" s="11" t="s">
         <v>1634</v>
       </c>
-      <c r="C79" t="s">
+      <c r="E79" s="10" t="s">
         <v>1635</v>
       </c>
-      <c r="D79" s="11" t="s">
+      <c r="F79" s="9" t="s">
         <v>1636</v>
       </c>
-      <c r="E79" s="10" t="s">
+      <c r="G79" s="9" t="s">
         <v>1637</v>
       </c>
-      <c r="F79" s="9" t="s">
+      <c r="H79" s="9" t="s">
         <v>1638</v>
       </c>
-      <c r="G79" s="9" t="s">
+      <c r="I79" s="9" t="s">
         <v>1639</v>
       </c>
-      <c r="H79" s="9" t="s">
+      <c r="J79" s="9" t="s">
         <v>1640</v>
       </c>
-      <c r="I79" s="9" t="s">
+      <c r="K79" t="s">
         <v>1641</v>
       </c>
-      <c r="J79" s="9" t="s">
+      <c r="L79" t="s">
         <v>1642</v>
       </c>
-      <c r="K79" t="s">
+      <c r="M79" t="s">
         <v>1643</v>
       </c>
-      <c r="L79" t="s">
+      <c r="N79" t="s">
         <v>1644</v>
       </c>
-      <c r="M79" t="s">
+      <c r="O79" t="s">
         <v>1645</v>
       </c>
-      <c r="N79" t="s">
+      <c r="P79" t="s">
         <v>1646</v>
       </c>
-      <c r="O79" t="s">
+      <c r="Q79" t="s">
         <v>1647</v>
       </c>
-      <c r="P79" t="s">
+      <c r="R79" t="s">
         <v>1648</v>
       </c>
-      <c r="Q79" t="s">
+      <c r="S79" t="s">
         <v>1649</v>
       </c>
-      <c r="R79" t="s">
+      <c r="T79" t="s">
         <v>1650</v>
       </c>
-      <c r="S79" t="s">
+      <c r="U79" t="s">
         <v>1651</v>
       </c>
-      <c r="T79" t="s">
+      <c r="V79" t="s">
         <v>1652</v>
-      </c>
-      <c r="U79" t="s">
-        <v>1653</v>
-      </c>
-      <c r="V79" t="s">
-        <v>1654</v>
       </c>
     </row>
     <row r="80" spans="1:22" x14ac:dyDescent="0.55000000000000004">
@@ -12042,67 +12046,67 @@
         <v>79</v>
       </c>
       <c r="B80" s="2" t="s">
+        <v>1653</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>1654</v>
+      </c>
+      <c r="D80" s="13" t="s">
         <v>1655</v>
       </c>
-      <c r="C80" s="2" t="s">
+      <c r="E80" s="10" t="s">
         <v>1656</v>
       </c>
-      <c r="D80" s="13" t="s">
+      <c r="F80" s="9" t="s">
         <v>1657</v>
       </c>
-      <c r="E80" s="10" t="s">
+      <c r="G80" s="9" t="s">
         <v>1658</v>
       </c>
-      <c r="F80" s="9" t="s">
+      <c r="H80" s="9" t="s">
         <v>1659</v>
       </c>
-      <c r="G80" s="9" t="s">
+      <c r="I80" s="9" t="s">
         <v>1660</v>
       </c>
-      <c r="H80" s="9" t="s">
+      <c r="J80" s="9" t="s">
         <v>1661</v>
       </c>
-      <c r="I80" s="9" t="s">
+      <c r="K80" t="s">
         <v>1662</v>
       </c>
-      <c r="J80" s="9" t="s">
+      <c r="L80" t="s">
+        <v>1194</v>
+      </c>
+      <c r="M80" t="s">
         <v>1663</v>
       </c>
-      <c r="K80" t="s">
+      <c r="N80" t="s">
         <v>1664</v>
       </c>
-      <c r="L80" t="s">
-        <v>1196</v>
-      </c>
-      <c r="M80" t="s">
+      <c r="O80" t="s">
         <v>1665</v>
       </c>
-      <c r="N80" t="s">
+      <c r="P80" t="s">
         <v>1666</v>
       </c>
-      <c r="O80" t="s">
+      <c r="Q80" t="s">
         <v>1667</v>
       </c>
-      <c r="P80" t="s">
+      <c r="R80" t="s">
         <v>1668</v>
       </c>
-      <c r="Q80" t="s">
+      <c r="S80" t="s">
         <v>1669</v>
       </c>
-      <c r="R80" t="s">
+      <c r="T80" t="s">
         <v>1670</v>
       </c>
-      <c r="S80" t="s">
+      <c r="U80" t="s">
         <v>1671</v>
       </c>
-      <c r="T80" t="s">
+      <c r="V80" t="s">
         <v>1672</v>
-      </c>
-      <c r="U80" t="s">
-        <v>1673</v>
-      </c>
-      <c r="V80" t="s">
-        <v>1674</v>
       </c>
     </row>
     <row r="81" spans="1:22" x14ac:dyDescent="0.55000000000000004">
@@ -12110,67 +12114,67 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
+        <v>1673</v>
+      </c>
+      <c r="C81" t="s">
+        <v>1674</v>
+      </c>
+      <c r="D81" s="13" t="s">
         <v>1675</v>
       </c>
-      <c r="C81" t="s">
+      <c r="E81" s="4" t="s">
         <v>1676</v>
       </c>
-      <c r="D81" s="13" t="s">
+      <c r="F81" s="9" t="s">
         <v>1677</v>
       </c>
-      <c r="E81" s="4" t="s">
+      <c r="G81" s="9" t="s">
         <v>1678</v>
       </c>
-      <c r="F81" s="9" t="s">
+      <c r="H81" s="9" t="s">
         <v>1679</v>
       </c>
-      <c r="G81" s="9" t="s">
+      <c r="I81" s="9" t="s">
         <v>1680</v>
       </c>
-      <c r="H81" s="9" t="s">
+      <c r="J81" s="9" t="s">
         <v>1681</v>
       </c>
-      <c r="I81" s="9" t="s">
+      <c r="K81" t="s">
         <v>1682</v>
       </c>
-      <c r="J81" s="9" t="s">
+      <c r="L81" t="s">
+        <v>1194</v>
+      </c>
+      <c r="M81" t="s">
         <v>1683</v>
       </c>
-      <c r="K81" t="s">
+      <c r="N81" t="s">
         <v>1684</v>
       </c>
-      <c r="L81" t="s">
-        <v>1196</v>
-      </c>
-      <c r="M81" t="s">
+      <c r="O81" t="s">
         <v>1685</v>
       </c>
-      <c r="N81" t="s">
+      <c r="P81" t="s">
         <v>1686</v>
       </c>
-      <c r="O81" t="s">
+      <c r="Q81" t="s">
         <v>1687</v>
       </c>
-      <c r="P81" t="s">
+      <c r="R81" t="s">
         <v>1688</v>
       </c>
-      <c r="Q81" t="s">
+      <c r="S81" t="s">
         <v>1689</v>
       </c>
-      <c r="R81" t="s">
+      <c r="T81" t="s">
         <v>1690</v>
       </c>
-      <c r="S81" t="s">
+      <c r="U81" t="s">
         <v>1691</v>
       </c>
-      <c r="T81" t="s">
+      <c r="V81" t="s">
         <v>1692</v>
-      </c>
-      <c r="U81" t="s">
-        <v>1693</v>
-      </c>
-      <c r="V81" t="s">
-        <v>1694</v>
       </c>
     </row>
     <row r="82" spans="1:22" x14ac:dyDescent="0.55000000000000004">
@@ -12178,67 +12182,67 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
+        <v>1693</v>
+      </c>
+      <c r="C82" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D82" s="11" t="s">
         <v>1695</v>
       </c>
-      <c r="C82" t="s">
+      <c r="E82" s="10" t="s">
         <v>1696</v>
       </c>
-      <c r="D82" s="11" t="s">
+      <c r="F82" s="9" t="s">
         <v>1697</v>
       </c>
-      <c r="E82" s="10" t="s">
+      <c r="G82" s="9" t="s">
         <v>1698</v>
       </c>
-      <c r="F82" s="9" t="s">
+      <c r="H82" s="9" t="s">
         <v>1699</v>
       </c>
-      <c r="G82" s="9" t="s">
+      <c r="I82" s="9" t="s">
         <v>1700</v>
       </c>
-      <c r="H82" s="9" t="s">
+      <c r="J82" s="9" t="s">
         <v>1701</v>
       </c>
-      <c r="I82" s="9" t="s">
+      <c r="K82" t="s">
         <v>1702</v>
       </c>
-      <c r="J82" s="9" t="s">
+      <c r="L82" t="s">
+        <v>1194</v>
+      </c>
+      <c r="M82" t="s">
         <v>1703</v>
       </c>
-      <c r="K82" t="s">
+      <c r="N82" t="s">
         <v>1704</v>
       </c>
-      <c r="L82" t="s">
-        <v>1196</v>
-      </c>
-      <c r="M82" t="s">
+      <c r="O82" t="s">
         <v>1705</v>
       </c>
-      <c r="N82" t="s">
+      <c r="P82" t="s">
         <v>1706</v>
       </c>
-      <c r="O82" t="s">
+      <c r="Q82" t="s">
         <v>1707</v>
       </c>
-      <c r="P82" t="s">
+      <c r="R82" t="s">
         <v>1708</v>
       </c>
-      <c r="Q82" t="s">
+      <c r="S82" t="s">
         <v>1709</v>
       </c>
-      <c r="R82" t="s">
+      <c r="T82" t="s">
         <v>1710</v>
       </c>
-      <c r="S82" t="s">
+      <c r="U82" t="s">
         <v>1711</v>
       </c>
-      <c r="T82" t="s">
+      <c r="V82" t="s">
         <v>1712</v>
-      </c>
-      <c r="U82" t="s">
-        <v>1713</v>
-      </c>
-      <c r="V82" t="s">
-        <v>1714</v>
       </c>
     </row>
     <row r="83" spans="1:22" x14ac:dyDescent="0.55000000000000004">
@@ -12246,67 +12250,67 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
+        <v>1713</v>
+      </c>
+      <c r="C83" t="s">
+        <v>1714</v>
+      </c>
+      <c r="D83" s="11" t="s">
         <v>1715</v>
       </c>
-      <c r="C83" t="s">
+      <c r="E83" s="10" t="s">
         <v>1716</v>
       </c>
-      <c r="D83" s="11" t="s">
+      <c r="F83" s="9" t="s">
         <v>1717</v>
       </c>
-      <c r="E83" s="10" t="s">
+      <c r="G83" s="9" t="s">
         <v>1718</v>
       </c>
-      <c r="F83" s="9" t="s">
+      <c r="H83" s="9" t="s">
         <v>1719</v>
       </c>
-      <c r="G83" s="9" t="s">
+      <c r="I83" s="9" t="s">
         <v>1720</v>
       </c>
-      <c r="H83" s="9" t="s">
+      <c r="J83" s="9" t="s">
         <v>1721</v>
       </c>
-      <c r="I83" s="9" t="s">
+      <c r="K83" t="s">
         <v>1722</v>
       </c>
-      <c r="J83" s="9" t="s">
+      <c r="L83" t="s">
+        <v>1194</v>
+      </c>
+      <c r="M83" t="s">
         <v>1723</v>
       </c>
-      <c r="K83" t="s">
+      <c r="N83" t="s">
         <v>1724</v>
       </c>
-      <c r="L83" t="s">
-        <v>1196</v>
-      </c>
-      <c r="M83" t="s">
+      <c r="O83" t="s">
         <v>1725</v>
       </c>
-      <c r="N83" t="s">
+      <c r="P83" t="s">
         <v>1726</v>
       </c>
-      <c r="O83" t="s">
+      <c r="Q83" t="s">
         <v>1727</v>
       </c>
-      <c r="P83" t="s">
+      <c r="R83" t="s">
         <v>1728</v>
       </c>
-      <c r="Q83" t="s">
+      <c r="S83" t="s">
         <v>1729</v>
       </c>
-      <c r="R83" t="s">
+      <c r="T83" t="s">
         <v>1730</v>
       </c>
-      <c r="S83" t="s">
+      <c r="U83" t="s">
         <v>1731</v>
       </c>
-      <c r="T83" t="s">
+      <c r="V83" t="s">
         <v>1732</v>
-      </c>
-      <c r="U83" t="s">
-        <v>1733</v>
-      </c>
-      <c r="V83" t="s">
-        <v>1734</v>
       </c>
     </row>
     <row r="84" spans="1:22" x14ac:dyDescent="0.55000000000000004">
@@ -12314,67 +12318,67 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C84" t="s">
+        <v>1734</v>
+      </c>
+      <c r="D84" s="11" t="s">
         <v>1735</v>
       </c>
-      <c r="C84" t="s">
+      <c r="E84" s="10" t="s">
         <v>1736</v>
       </c>
-      <c r="D84" s="11" t="s">
+      <c r="F84" s="9" t="s">
         <v>1737</v>
       </c>
-      <c r="E84" s="10" t="s">
+      <c r="G84" s="9" t="s">
         <v>1738</v>
       </c>
-      <c r="F84" s="9" t="s">
+      <c r="H84" s="9" t="s">
         <v>1739</v>
       </c>
-      <c r="G84" s="9" t="s">
+      <c r="I84" s="9" t="s">
         <v>1740</v>
       </c>
-      <c r="H84" s="9" t="s">
+      <c r="J84" s="9" t="s">
         <v>1741</v>
       </c>
-      <c r="I84" s="9" t="s">
+      <c r="K84" t="s">
         <v>1742</v>
       </c>
-      <c r="J84" s="9" t="s">
+      <c r="L84" t="s">
+        <v>1194</v>
+      </c>
+      <c r="M84" t="s">
         <v>1743</v>
       </c>
-      <c r="K84" t="s">
+      <c r="N84" t="s">
         <v>1744</v>
       </c>
-      <c r="L84" t="s">
-        <v>1196</v>
-      </c>
-      <c r="M84" t="s">
+      <c r="O84" t="s">
         <v>1745</v>
       </c>
-      <c r="N84" t="s">
+      <c r="P84" t="s">
         <v>1746</v>
       </c>
-      <c r="O84" t="s">
+      <c r="Q84" t="s">
         <v>1747</v>
       </c>
-      <c r="P84" t="s">
+      <c r="R84" t="s">
         <v>1748</v>
       </c>
-      <c r="Q84" t="s">
+      <c r="S84" t="s">
         <v>1749</v>
       </c>
-      <c r="R84" t="s">
+      <c r="T84" t="s">
         <v>1750</v>
       </c>
-      <c r="S84" t="s">
+      <c r="U84" t="s">
         <v>1751</v>
       </c>
-      <c r="T84" t="s">
+      <c r="V84" t="s">
         <v>1752</v>
-      </c>
-      <c r="U84" t="s">
-        <v>1753</v>
-      </c>
-      <c r="V84" t="s">
-        <v>1754</v>
       </c>
     </row>
     <row r="85" spans="1:22" x14ac:dyDescent="0.55000000000000004">
@@ -12382,67 +12386,67 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
+        <v>1753</v>
+      </c>
+      <c r="C85" t="s">
+        <v>1754</v>
+      </c>
+      <c r="D85" s="13" t="s">
         <v>1755</v>
       </c>
-      <c r="C85" t="s">
+      <c r="E85" s="4" t="s">
         <v>1756</v>
       </c>
-      <c r="D85" s="13" t="s">
+      <c r="F85" s="9" t="s">
         <v>1757</v>
       </c>
-      <c r="E85" s="4" t="s">
+      <c r="G85" s="9" t="s">
         <v>1758</v>
       </c>
-      <c r="F85" s="9" t="s">
+      <c r="H85" s="9" t="s">
         <v>1759</v>
       </c>
-      <c r="G85" s="9" t="s">
+      <c r="I85" s="9" t="s">
         <v>1760</v>
       </c>
-      <c r="H85" s="9" t="s">
+      <c r="J85" s="9" t="s">
         <v>1761</v>
       </c>
-      <c r="I85" s="9" t="s">
+      <c r="K85" t="s">
         <v>1762</v>
       </c>
-      <c r="J85" s="9" t="s">
+      <c r="L85" t="s">
         <v>1763</v>
       </c>
-      <c r="K85" t="s">
+      <c r="M85" t="s">
         <v>1764</v>
       </c>
-      <c r="L85" t="s">
+      <c r="N85" t="s">
         <v>1765</v>
       </c>
-      <c r="M85" t="s">
+      <c r="O85" t="s">
         <v>1766</v>
       </c>
-      <c r="N85" t="s">
+      <c r="P85" t="s">
         <v>1767</v>
       </c>
-      <c r="O85" t="s">
+      <c r="Q85" t="s">
         <v>1768</v>
       </c>
-      <c r="P85" t="s">
+      <c r="R85" t="s">
         <v>1769</v>
       </c>
-      <c r="Q85" t="s">
+      <c r="S85" t="s">
         <v>1770</v>
       </c>
-      <c r="R85" t="s">
+      <c r="T85" t="s">
         <v>1771</v>
       </c>
-      <c r="S85" t="s">
+      <c r="U85" t="s">
         <v>1772</v>
       </c>
-      <c r="T85" t="s">
+      <c r="V85" t="s">
         <v>1773</v>
-      </c>
-      <c r="U85" t="s">
-        <v>1774</v>
-      </c>
-      <c r="V85" t="s">
-        <v>1775</v>
       </c>
     </row>
     <row r="86" spans="1:22" x14ac:dyDescent="0.55000000000000004">
@@ -12450,67 +12454,67 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
+        <v>1774</v>
+      </c>
+      <c r="C86" t="s">
+        <v>1775</v>
+      </c>
+      <c r="D86" s="11" t="s">
         <v>1776</v>
       </c>
-      <c r="C86" t="s">
+      <c r="E86" s="4" t="s">
         <v>1777</v>
       </c>
-      <c r="D86" s="11" t="s">
+      <c r="F86" s="9" t="s">
         <v>1778</v>
       </c>
-      <c r="E86" s="4" t="s">
+      <c r="G86" s="9" t="s">
         <v>1779</v>
       </c>
-      <c r="F86" s="9" t="s">
+      <c r="H86" s="9" t="s">
         <v>1780</v>
       </c>
-      <c r="G86" s="9" t="s">
+      <c r="I86" s="9" t="s">
         <v>1781</v>
       </c>
-      <c r="H86" s="9" t="s">
+      <c r="J86" s="9" t="s">
         <v>1782</v>
       </c>
-      <c r="I86" s="9" t="s">
+      <c r="K86" t="s">
         <v>1783</v>
       </c>
-      <c r="J86" s="9" t="s">
+      <c r="L86" t="s">
         <v>1784</v>
       </c>
-      <c r="K86" t="s">
+      <c r="M86" t="s">
         <v>1785</v>
       </c>
-      <c r="L86" t="s">
+      <c r="N86" t="s">
         <v>1786</v>
       </c>
-      <c r="M86" t="s">
+      <c r="O86" t="s">
         <v>1787</v>
       </c>
-      <c r="N86" t="s">
+      <c r="P86" t="s">
         <v>1788</v>
       </c>
-      <c r="O86" t="s">
+      <c r="Q86" t="s">
         <v>1789</v>
       </c>
-      <c r="P86" t="s">
+      <c r="R86" t="s">
         <v>1790</v>
       </c>
-      <c r="Q86" t="s">
+      <c r="S86" t="s">
         <v>1791</v>
       </c>
-      <c r="R86" t="s">
+      <c r="T86" t="s">
         <v>1792</v>
       </c>
-      <c r="S86" t="s">
+      <c r="U86" t="s">
         <v>1793</v>
       </c>
-      <c r="T86" t="s">
+      <c r="V86" t="s">
         <v>1794</v>
-      </c>
-      <c r="U86" t="s">
-        <v>1795</v>
-      </c>
-      <c r="V86" t="s">
-        <v>1796</v>
       </c>
     </row>
     <row r="87" spans="1:22" x14ac:dyDescent="0.55000000000000004">
@@ -12518,67 +12522,67 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
+        <v>1795</v>
+      </c>
+      <c r="C87" t="s">
+        <v>1796</v>
+      </c>
+      <c r="D87" s="11" t="s">
         <v>1797</v>
       </c>
-      <c r="C87" t="s">
+      <c r="E87" s="4" t="s">
         <v>1798</v>
       </c>
-      <c r="D87" s="11" t="s">
+      <c r="F87" s="9" t="s">
         <v>1799</v>
       </c>
-      <c r="E87" s="4" t="s">
+      <c r="G87" s="9" t="s">
         <v>1800</v>
       </c>
-      <c r="F87" s="9" t="s">
+      <c r="H87" s="9" t="s">
         <v>1801</v>
       </c>
-      <c r="G87" s="9" t="s">
+      <c r="I87" s="9" t="s">
         <v>1802</v>
       </c>
-      <c r="H87" s="9" t="s">
+      <c r="J87" s="9" t="s">
         <v>1803</v>
       </c>
-      <c r="I87" s="9" t="s">
+      <c r="K87" t="s">
         <v>1804</v>
       </c>
-      <c r="J87" s="9" t="s">
+      <c r="L87" t="s">
+        <v>1194</v>
+      </c>
+      <c r="M87" t="s">
         <v>1805</v>
       </c>
-      <c r="K87" t="s">
+      <c r="N87" t="s">
         <v>1806</v>
       </c>
-      <c r="L87" t="s">
-        <v>1196</v>
-      </c>
-      <c r="M87" t="s">
+      <c r="O87" t="s">
         <v>1807</v>
       </c>
-      <c r="N87" t="s">
+      <c r="P87" t="s">
         <v>1808</v>
       </c>
-      <c r="O87" t="s">
+      <c r="Q87" t="s">
         <v>1809</v>
       </c>
-      <c r="P87" t="s">
+      <c r="R87" t="s">
         <v>1810</v>
       </c>
-      <c r="Q87" t="s">
+      <c r="S87" t="s">
         <v>1811</v>
       </c>
-      <c r="R87" t="s">
+      <c r="T87" t="s">
         <v>1812</v>
       </c>
-      <c r="S87" t="s">
+      <c r="U87" t="s">
         <v>1813</v>
       </c>
-      <c r="T87" t="s">
+      <c r="V87" t="s">
         <v>1814</v>
-      </c>
-      <c r="U87" t="s">
-        <v>1815</v>
-      </c>
-      <c r="V87" t="s">
-        <v>1816</v>
       </c>
     </row>
     <row r="88" spans="1:22" x14ac:dyDescent="0.55000000000000004">
@@ -12586,67 +12590,67 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
+        <v>1815</v>
+      </c>
+      <c r="C88" t="s">
+        <v>1816</v>
+      </c>
+      <c r="D88" s="11" t="s">
         <v>1817</v>
       </c>
-      <c r="C88" t="s">
+      <c r="E88" s="4" t="s">
         <v>1818</v>
       </c>
-      <c r="D88" s="11" t="s">
+      <c r="F88" s="9" t="s">
         <v>1819</v>
       </c>
-      <c r="E88" s="4" t="s">
+      <c r="G88" s="9" t="s">
         <v>1820</v>
       </c>
-      <c r="F88" s="9" t="s">
+      <c r="H88" s="9" t="s">
         <v>1821</v>
       </c>
-      <c r="G88" s="9" t="s">
+      <c r="I88" s="9" t="s">
         <v>1822</v>
       </c>
-      <c r="H88" s="9" t="s">
+      <c r="J88" s="9" t="s">
         <v>1823</v>
       </c>
-      <c r="I88" s="9" t="s">
+      <c r="K88" t="s">
         <v>1824</v>
       </c>
-      <c r="J88" s="9" t="s">
+      <c r="L88" t="s">
         <v>1825</v>
       </c>
-      <c r="K88" t="s">
+      <c r="M88" t="s">
         <v>1826</v>
       </c>
-      <c r="L88" t="s">
+      <c r="N88" t="s">
         <v>1827</v>
       </c>
-      <c r="M88" t="s">
+      <c r="O88" t="s">
         <v>1828</v>
       </c>
-      <c r="N88" t="s">
+      <c r="P88" t="s">
         <v>1829</v>
       </c>
-      <c r="O88" t="s">
+      <c r="Q88" t="s">
         <v>1830</v>
       </c>
-      <c r="P88" t="s">
+      <c r="R88" t="s">
         <v>1831</v>
       </c>
-      <c r="Q88" t="s">
+      <c r="S88" t="s">
         <v>1832</v>
       </c>
-      <c r="R88" t="s">
+      <c r="T88" t="s">
         <v>1833</v>
       </c>
-      <c r="S88" t="s">
+      <c r="U88" t="s">
         <v>1834</v>
       </c>
-      <c r="T88" t="s">
+      <c r="V88" t="s">
         <v>1835</v>
-      </c>
-      <c r="U88" t="s">
-        <v>1836</v>
-      </c>
-      <c r="V88" t="s">
-        <v>1837</v>
       </c>
     </row>
     <row r="89" spans="1:22" x14ac:dyDescent="0.55000000000000004">
@@ -12654,67 +12658,67 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
+        <v>1836</v>
+      </c>
+      <c r="C89" t="s">
+        <v>1837</v>
+      </c>
+      <c r="D89" s="11" t="s">
         <v>1838</v>
       </c>
-      <c r="C89" t="s">
+      <c r="E89" s="10" t="s">
         <v>1839</v>
       </c>
-      <c r="D89" s="11" t="s">
+      <c r="F89" s="9" t="s">
         <v>1840</v>
       </c>
-      <c r="E89" s="10" t="s">
+      <c r="G89" s="9" t="s">
         <v>1841</v>
       </c>
-      <c r="F89" s="9" t="s">
+      <c r="H89" s="9" t="s">
         <v>1842</v>
       </c>
-      <c r="G89" s="9" t="s">
+      <c r="I89" s="9" t="s">
         <v>1843</v>
       </c>
-      <c r="H89" s="9" t="s">
+      <c r="J89" s="9" t="s">
         <v>1844</v>
       </c>
-      <c r="I89" s="9" t="s">
+      <c r="K89" t="s">
         <v>1845</v>
       </c>
-      <c r="J89" s="9" t="s">
+      <c r="L89" t="s">
         <v>1846</v>
       </c>
-      <c r="K89" t="s">
+      <c r="M89" t="s">
         <v>1847</v>
       </c>
-      <c r="L89" t="s">
+      <c r="N89" t="s">
         <v>1848</v>
       </c>
-      <c r="M89" t="s">
+      <c r="O89" t="s">
         <v>1849</v>
       </c>
-      <c r="N89" t="s">
+      <c r="P89" t="s">
         <v>1850</v>
       </c>
-      <c r="O89" t="s">
+      <c r="Q89" t="s">
         <v>1851</v>
       </c>
-      <c r="P89" t="s">
+      <c r="R89" t="s">
         <v>1852</v>
       </c>
-      <c r="Q89" t="s">
+      <c r="S89" t="s">
         <v>1853</v>
       </c>
-      <c r="R89" t="s">
+      <c r="T89" t="s">
         <v>1854</v>
       </c>
-      <c r="S89" t="s">
+      <c r="U89" t="s">
         <v>1855</v>
       </c>
-      <c r="T89" t="s">
+      <c r="V89" t="s">
         <v>1856</v>
-      </c>
-      <c r="U89" t="s">
-        <v>1857</v>
-      </c>
-      <c r="V89" t="s">
-        <v>1858</v>
       </c>
     </row>
     <row r="90" spans="1:22" x14ac:dyDescent="0.55000000000000004">
@@ -12722,67 +12726,67 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
+        <v>1857</v>
+      </c>
+      <c r="C90" t="s">
+        <v>1858</v>
+      </c>
+      <c r="D90" s="11" t="s">
         <v>1859</v>
       </c>
-      <c r="C90" t="s">
+      <c r="E90" s="4" t="s">
         <v>1860</v>
       </c>
-      <c r="D90" s="11" t="s">
+      <c r="F90" s="9" t="s">
         <v>1861</v>
       </c>
-      <c r="E90" s="4" t="s">
+      <c r="G90" s="9" t="s">
         <v>1862</v>
       </c>
-      <c r="F90" s="9" t="s">
+      <c r="H90" s="9" t="s">
         <v>1863</v>
       </c>
-      <c r="G90" s="9" t="s">
+      <c r="I90" s="9" t="s">
         <v>1864</v>
       </c>
-      <c r="H90" s="9" t="s">
+      <c r="J90" s="9" t="s">
         <v>1865</v>
       </c>
-      <c r="I90" s="9" t="s">
+      <c r="K90" t="s">
         <v>1866</v>
       </c>
-      <c r="J90" s="9" t="s">
+      <c r="L90" t="s">
         <v>1867</v>
       </c>
-      <c r="K90" t="s">
+      <c r="M90" t="s">
         <v>1868</v>
       </c>
-      <c r="L90" t="s">
+      <c r="N90" t="s">
         <v>1869</v>
       </c>
-      <c r="M90" t="s">
+      <c r="O90" t="s">
         <v>1870</v>
       </c>
-      <c r="N90" t="s">
+      <c r="P90" t="s">
         <v>1871</v>
       </c>
-      <c r="O90" t="s">
+      <c r="Q90" t="s">
         <v>1872</v>
       </c>
-      <c r="P90" t="s">
+      <c r="R90" t="s">
         <v>1873</v>
       </c>
-      <c r="Q90" t="s">
+      <c r="S90" t="s">
         <v>1874</v>
       </c>
-      <c r="R90" t="s">
+      <c r="T90" t="s">
         <v>1875</v>
       </c>
-      <c r="S90" t="s">
+      <c r="U90" t="s">
         <v>1876</v>
       </c>
-      <c r="T90" t="s">
+      <c r="V90" t="s">
         <v>1877</v>
-      </c>
-      <c r="U90" t="s">
-        <v>1878</v>
-      </c>
-      <c r="V90" t="s">
-        <v>1879</v>
       </c>
     </row>
     <row r="91" spans="1:22" x14ac:dyDescent="0.55000000000000004">
@@ -12790,67 +12794,67 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
+        <v>1878</v>
+      </c>
+      <c r="C91" t="s">
+        <v>1879</v>
+      </c>
+      <c r="D91" s="11" t="s">
         <v>1880</v>
       </c>
-      <c r="C91" t="s">
+      <c r="E91" s="4" t="s">
         <v>1881</v>
       </c>
-      <c r="D91" s="11" t="s">
+      <c r="F91" s="9" t="s">
         <v>1882</v>
       </c>
-      <c r="E91" s="4" t="s">
+      <c r="G91" s="9" t="s">
         <v>1883</v>
       </c>
-      <c r="F91" s="9" t="s">
+      <c r="H91" s="9" t="s">
         <v>1884</v>
       </c>
-      <c r="G91" s="9" t="s">
+      <c r="I91" s="9" t="s">
         <v>1885</v>
       </c>
-      <c r="H91" s="9" t="s">
+      <c r="J91" s="9" t="s">
         <v>1886</v>
       </c>
-      <c r="I91" s="9" t="s">
+      <c r="K91" t="s">
         <v>1887</v>
       </c>
-      <c r="J91" s="9" t="s">
+      <c r="L91" t="s">
         <v>1888</v>
       </c>
-      <c r="K91" t="s">
+      <c r="M91" t="s">
         <v>1889</v>
       </c>
-      <c r="L91" t="s">
+      <c r="N91" t="s">
         <v>1890</v>
       </c>
-      <c r="M91" t="s">
+      <c r="O91" t="s">
         <v>1891</v>
       </c>
-      <c r="N91" t="s">
+      <c r="P91" t="s">
         <v>1892</v>
       </c>
-      <c r="O91" t="s">
+      <c r="Q91" t="s">
         <v>1893</v>
       </c>
-      <c r="P91" t="s">
+      <c r="R91" t="s">
         <v>1894</v>
       </c>
-      <c r="Q91" t="s">
+      <c r="S91" t="s">
         <v>1895</v>
       </c>
-      <c r="R91" t="s">
+      <c r="T91" t="s">
         <v>1896</v>
       </c>
-      <c r="S91" t="s">
+      <c r="U91" t="s">
         <v>1897</v>
       </c>
-      <c r="T91" t="s">
+      <c r="V91" t="s">
         <v>1898</v>
-      </c>
-      <c r="U91" t="s">
-        <v>1899</v>
-      </c>
-      <c r="V91" t="s">
-        <v>1900</v>
       </c>
     </row>
     <row r="92" spans="1:22" x14ac:dyDescent="0.55000000000000004">
@@ -12858,67 +12862,67 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C92" t="s">
+        <v>1900</v>
+      </c>
+      <c r="D92" s="11" t="s">
+        <v>1755</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>1756</v>
+      </c>
+      <c r="F92" s="9" t="s">
         <v>1901</v>
       </c>
-      <c r="C92" t="s">
+      <c r="G92" s="9" t="s">
         <v>1902</v>
       </c>
-      <c r="D92" s="11" t="s">
-        <v>1757</v>
-      </c>
-      <c r="E92" s="4" t="s">
-        <v>1758</v>
-      </c>
-      <c r="F92" s="9" t="s">
+      <c r="H92" s="9" t="s">
         <v>1903</v>
       </c>
-      <c r="G92" s="9" t="s">
+      <c r="I92" s="9" t="s">
         <v>1904</v>
       </c>
-      <c r="H92" s="9" t="s">
+      <c r="J92" s="9" t="s">
         <v>1905</v>
       </c>
-      <c r="I92" s="9" t="s">
+      <c r="K92" t="s">
         <v>1906</v>
       </c>
-      <c r="J92" s="9" t="s">
+      <c r="L92" t="s">
         <v>1907</v>
       </c>
-      <c r="K92" t="s">
+      <c r="M92" t="s">
         <v>1908</v>
       </c>
-      <c r="L92" t="s">
+      <c r="N92" t="s">
         <v>1909</v>
       </c>
-      <c r="M92" t="s">
+      <c r="O92" t="s">
         <v>1910</v>
       </c>
-      <c r="N92" t="s">
+      <c r="P92" t="s">
         <v>1911</v>
       </c>
-      <c r="O92" t="s">
+      <c r="Q92" t="s">
         <v>1912</v>
       </c>
-      <c r="P92" t="s">
+      <c r="R92" t="s">
         <v>1913</v>
       </c>
-      <c r="Q92" t="s">
+      <c r="S92" t="s">
         <v>1914</v>
       </c>
-      <c r="R92" t="s">
+      <c r="T92" t="s">
         <v>1915</v>
       </c>
-      <c r="S92" t="s">
+      <c r="U92" t="s">
         <v>1916</v>
       </c>
-      <c r="T92" t="s">
+      <c r="V92" t="s">
         <v>1917</v>
-      </c>
-      <c r="U92" t="s">
-        <v>1918</v>
-      </c>
-      <c r="V92" t="s">
-        <v>1919</v>
       </c>
     </row>
     <row r="93" spans="1:22" x14ac:dyDescent="0.55000000000000004">
@@ -12926,67 +12930,67 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
+        <v>1918</v>
+      </c>
+      <c r="C93" t="s">
+        <v>1919</v>
+      </c>
+      <c r="D93" s="11" t="s">
         <v>1920</v>
       </c>
-      <c r="C93" t="s">
+      <c r="E93" s="4" t="s">
         <v>1921</v>
       </c>
-      <c r="D93" s="11" t="s">
+      <c r="F93" s="9" t="s">
         <v>1922</v>
       </c>
-      <c r="E93" s="4" t="s">
+      <c r="G93" s="9" t="s">
         <v>1923</v>
       </c>
-      <c r="F93" s="9" t="s">
+      <c r="H93" s="9" t="s">
         <v>1924</v>
       </c>
-      <c r="G93" s="9" t="s">
+      <c r="I93" s="9" t="s">
         <v>1925</v>
       </c>
-      <c r="H93" s="9" t="s">
+      <c r="J93" s="9" t="s">
         <v>1926</v>
       </c>
-      <c r="I93" s="9" t="s">
+      <c r="K93" t="s">
         <v>1927</v>
       </c>
-      <c r="J93" s="9" t="s">
+      <c r="L93" t="s">
         <v>1928</v>
       </c>
-      <c r="K93" t="s">
+      <c r="M93" t="s">
         <v>1929</v>
       </c>
-      <c r="L93" t="s">
+      <c r="N93" t="s">
         <v>1930</v>
       </c>
-      <c r="M93" t="s">
+      <c r="O93" t="s">
         <v>1931</v>
       </c>
-      <c r="N93" t="s">
+      <c r="P93" t="s">
         <v>1932</v>
       </c>
-      <c r="O93" t="s">
+      <c r="Q93" t="s">
         <v>1933</v>
       </c>
-      <c r="P93" t="s">
+      <c r="R93" t="s">
         <v>1934</v>
       </c>
-      <c r="Q93" t="s">
+      <c r="S93" t="s">
         <v>1935</v>
       </c>
-      <c r="R93" t="s">
+      <c r="T93" t="s">
         <v>1936</v>
       </c>
-      <c r="S93" t="s">
+      <c r="U93" t="s">
         <v>1937</v>
       </c>
-      <c r="T93" t="s">
+      <c r="V93" t="s">
         <v>1938</v>
-      </c>
-      <c r="U93" t="s">
-        <v>1939</v>
-      </c>
-      <c r="V93" t="s">
-        <v>1940</v>
       </c>
     </row>
     <row r="94" spans="1:22" x14ac:dyDescent="0.55000000000000004">
@@ -12994,67 +12998,67 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
+        <v>1939</v>
+      </c>
+      <c r="C94" t="s">
+        <v>1940</v>
+      </c>
+      <c r="D94" s="11" t="s">
         <v>1941</v>
       </c>
-      <c r="C94" t="s">
+      <c r="E94" s="10" t="s">
         <v>1942</v>
       </c>
-      <c r="D94" s="11" t="s">
+      <c r="F94" s="9" t="s">
         <v>1943</v>
       </c>
-      <c r="E94" s="10" t="s">
+      <c r="G94" s="9" t="s">
         <v>1944</v>
       </c>
-      <c r="F94" s="9" t="s">
+      <c r="H94" s="9" t="s">
         <v>1945</v>
       </c>
-      <c r="G94" s="9" t="s">
+      <c r="I94" s="9" t="s">
         <v>1946</v>
       </c>
-      <c r="H94" s="9" t="s">
+      <c r="J94" s="9" t="s">
         <v>1947</v>
       </c>
-      <c r="I94" s="9" t="s">
+      <c r="K94" t="s">
         <v>1948</v>
       </c>
-      <c r="J94" s="9" t="s">
+      <c r="L94" t="s">
         <v>1949</v>
       </c>
-      <c r="K94" t="s">
+      <c r="M94" t="s">
         <v>1950</v>
       </c>
-      <c r="L94" t="s">
+      <c r="N94" t="s">
         <v>1951</v>
       </c>
-      <c r="M94" t="s">
+      <c r="O94" t="s">
         <v>1952</v>
       </c>
-      <c r="N94" t="s">
+      <c r="P94" t="s">
         <v>1953</v>
       </c>
-      <c r="O94" t="s">
+      <c r="Q94" t="s">
         <v>1954</v>
       </c>
-      <c r="P94" t="s">
+      <c r="R94" t="s">
         <v>1955</v>
       </c>
-      <c r="Q94" t="s">
+      <c r="S94" t="s">
         <v>1956</v>
       </c>
-      <c r="R94" t="s">
+      <c r="T94" t="s">
         <v>1957</v>
       </c>
-      <c r="S94" t="s">
+      <c r="U94" t="s">
         <v>1958</v>
       </c>
-      <c r="T94" t="s">
+      <c r="V94" t="s">
         <v>1959</v>
-      </c>
-      <c r="U94" t="s">
-        <v>1960</v>
-      </c>
-      <c r="V94" t="s">
-        <v>1961</v>
       </c>
     </row>
     <row r="95" spans="1:22" x14ac:dyDescent="0.55000000000000004">
@@ -13062,67 +13066,67 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
+        <v>1960</v>
+      </c>
+      <c r="C95" t="s">
+        <v>1961</v>
+      </c>
+      <c r="D95" s="11" t="s">
         <v>1962</v>
       </c>
-      <c r="C95" t="s">
+      <c r="E95" s="4" t="s">
         <v>1963</v>
       </c>
-      <c r="D95" s="11" t="s">
+      <c r="F95" s="9" t="s">
         <v>1964</v>
       </c>
-      <c r="E95" s="4" t="s">
+      <c r="G95" s="9" t="s">
         <v>1965</v>
       </c>
-      <c r="F95" s="9" t="s">
+      <c r="H95" s="9" t="s">
         <v>1966</v>
       </c>
-      <c r="G95" s="9" t="s">
+      <c r="I95" s="9" t="s">
         <v>1967</v>
       </c>
-      <c r="H95" s="9" t="s">
+      <c r="J95" s="9" t="s">
         <v>1968</v>
       </c>
-      <c r="I95" s="9" t="s">
+      <c r="K95" t="s">
         <v>1969</v>
       </c>
-      <c r="J95" s="9" t="s">
+      <c r="L95" t="s">
         <v>1970</v>
       </c>
-      <c r="K95" t="s">
+      <c r="M95" t="s">
         <v>1971</v>
       </c>
-      <c r="L95" t="s">
+      <c r="N95" t="s">
         <v>1972</v>
       </c>
-      <c r="M95" t="s">
+      <c r="O95" t="s">
         <v>1973</v>
       </c>
-      <c r="N95" t="s">
+      <c r="P95" t="s">
         <v>1974</v>
       </c>
-      <c r="O95" t="s">
+      <c r="Q95" t="s">
         <v>1975</v>
       </c>
-      <c r="P95" t="s">
+      <c r="R95" t="s">
         <v>1976</v>
       </c>
-      <c r="Q95" t="s">
+      <c r="S95" t="s">
         <v>1977</v>
       </c>
-      <c r="R95" t="s">
+      <c r="T95" t="s">
         <v>1978</v>
       </c>
-      <c r="S95" t="s">
+      <c r="U95" t="s">
         <v>1979</v>
       </c>
-      <c r="T95" t="s">
+      <c r="V95" t="s">
         <v>1980</v>
-      </c>
-      <c r="U95" t="s">
-        <v>1981</v>
-      </c>
-      <c r="V95" t="s">
-        <v>1982</v>
       </c>
     </row>
     <row r="96" spans="1:22" x14ac:dyDescent="0.55000000000000004">
@@ -13130,67 +13134,67 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
+        <v>1981</v>
+      </c>
+      <c r="C96" t="s">
+        <v>1982</v>
+      </c>
+      <c r="D96" s="11" t="s">
         <v>1983</v>
       </c>
-      <c r="C96" t="s">
+      <c r="E96" s="4" t="s">
         <v>1984</v>
       </c>
-      <c r="D96" s="11" t="s">
+      <c r="F96" s="9" t="s">
         <v>1985</v>
       </c>
-      <c r="E96" s="4" t="s">
+      <c r="G96" s="9" t="s">
+        <v>1965</v>
+      </c>
+      <c r="H96" s="9" t="s">
         <v>1986</v>
       </c>
-      <c r="F96" s="9" t="s">
+      <c r="I96" s="9" t="s">
         <v>1987</v>
       </c>
-      <c r="G96" s="9" t="s">
-        <v>1967</v>
-      </c>
-      <c r="H96" s="9" t="s">
+      <c r="J96" s="9" t="s">
         <v>1988</v>
       </c>
-      <c r="I96" s="9" t="s">
+      <c r="K96" t="s">
         <v>1989</v>
       </c>
-      <c r="J96" s="9" t="s">
+      <c r="L96" t="s">
         <v>1990</v>
       </c>
-      <c r="K96" t="s">
+      <c r="M96" t="s">
         <v>1991</v>
       </c>
-      <c r="L96" t="s">
+      <c r="N96" t="s">
         <v>1992</v>
       </c>
-      <c r="M96" t="s">
+      <c r="O96" t="s">
         <v>1993</v>
       </c>
-      <c r="N96" t="s">
+      <c r="P96" t="s">
         <v>1994</v>
       </c>
-      <c r="O96" t="s">
+      <c r="Q96" t="s">
         <v>1995</v>
       </c>
-      <c r="P96" t="s">
+      <c r="R96" t="s">
         <v>1996</v>
       </c>
-      <c r="Q96" t="s">
+      <c r="S96" t="s">
         <v>1997</v>
       </c>
-      <c r="R96" t="s">
+      <c r="T96" t="s">
         <v>1998</v>
       </c>
-      <c r="S96" t="s">
+      <c r="U96" t="s">
         <v>1999</v>
       </c>
-      <c r="T96" t="s">
+      <c r="V96" t="s">
         <v>2000</v>
-      </c>
-      <c r="U96" t="s">
-        <v>2001</v>
-      </c>
-      <c r="V96" t="s">
-        <v>2002</v>
       </c>
     </row>
     <row r="97" spans="1:22" x14ac:dyDescent="0.55000000000000004">
@@ -13198,67 +13202,67 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
+        <v>2001</v>
+      </c>
+      <c r="C97" t="s">
+        <v>2002</v>
+      </c>
+      <c r="D97" s="11" t="s">
         <v>2003</v>
       </c>
-      <c r="C97" t="s">
+      <c r="E97" s="4" t="s">
         <v>2004</v>
       </c>
-      <c r="D97" s="11" t="s">
+      <c r="F97" s="9" t="s">
         <v>2005</v>
       </c>
-      <c r="E97" s="4" t="s">
+      <c r="G97" s="9" t="s">
         <v>2006</v>
       </c>
-      <c r="F97" s="9" t="s">
+      <c r="H97" s="9" t="s">
         <v>2007</v>
       </c>
-      <c r="G97" s="9" t="s">
+      <c r="I97" s="9" t="s">
         <v>2008</v>
       </c>
-      <c r="H97" s="9" t="s">
+      <c r="J97" s="9" t="s">
         <v>2009</v>
       </c>
-      <c r="I97" s="9" t="s">
+      <c r="K97" t="s">
         <v>2010</v>
       </c>
-      <c r="J97" s="9" t="s">
+      <c r="L97" t="s">
         <v>2011</v>
       </c>
-      <c r="K97" t="s">
+      <c r="M97" t="s">
         <v>2012</v>
       </c>
-      <c r="L97" t="s">
+      <c r="N97" t="s">
         <v>2013</v>
       </c>
-      <c r="M97" t="s">
+      <c r="O97" t="s">
         <v>2014</v>
       </c>
-      <c r="N97" t="s">
+      <c r="P97" t="s">
         <v>2015</v>
       </c>
-      <c r="O97" t="s">
+      <c r="Q97" t="s">
         <v>2016</v>
       </c>
-      <c r="P97" t="s">
+      <c r="R97" t="s">
         <v>2017</v>
       </c>
-      <c r="Q97" t="s">
+      <c r="S97" t="s">
         <v>2018</v>
       </c>
-      <c r="R97" t="s">
+      <c r="T97" t="s">
         <v>2019</v>
       </c>
-      <c r="S97" t="s">
+      <c r="U97" t="s">
         <v>2020</v>
       </c>
-      <c r="T97" t="s">
+      <c r="V97" t="s">
         <v>2021</v>
-      </c>
-      <c r="U97" t="s">
-        <v>2022</v>
-      </c>
-      <c r="V97" t="s">
-        <v>2023</v>
       </c>
     </row>
     <row r="98" spans="1:22" x14ac:dyDescent="0.55000000000000004">
@@ -13266,67 +13270,67 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
+        <v>2022</v>
+      </c>
+      <c r="C98" t="s">
+        <v>2023</v>
+      </c>
+      <c r="D98" s="11" t="s">
         <v>2024</v>
       </c>
-      <c r="C98" t="s">
+      <c r="E98" s="4" t="s">
         <v>2025</v>
       </c>
-      <c r="D98" s="11" t="s">
+      <c r="F98" s="9" t="s">
         <v>2026</v>
       </c>
-      <c r="E98" s="4" t="s">
+      <c r="G98" s="9" t="s">
         <v>2027</v>
       </c>
-      <c r="F98" s="9" t="s">
+      <c r="H98" s="9" t="s">
         <v>2028</v>
       </c>
-      <c r="G98" s="9" t="s">
+      <c r="I98" s="9" t="s">
         <v>2029</v>
       </c>
-      <c r="H98" s="9" t="s">
+      <c r="J98" s="9" t="s">
         <v>2030</v>
       </c>
-      <c r="I98" s="9" t="s">
+      <c r="K98" t="s">
         <v>2031</v>
       </c>
-      <c r="J98" s="9" t="s">
+      <c r="L98" t="s">
         <v>2032</v>
       </c>
-      <c r="K98" t="s">
+      <c r="M98" t="s">
         <v>2033</v>
       </c>
-      <c r="L98" t="s">
+      <c r="N98" t="s">
         <v>2034</v>
       </c>
-      <c r="M98" t="s">
+      <c r="O98" t="s">
         <v>2035</v>
       </c>
-      <c r="N98" t="s">
+      <c r="P98" t="s">
         <v>2036</v>
       </c>
-      <c r="O98" t="s">
+      <c r="Q98" t="s">
         <v>2037</v>
       </c>
-      <c r="P98" t="s">
+      <c r="R98" t="s">
         <v>2038</v>
       </c>
-      <c r="Q98" t="s">
+      <c r="S98" t="s">
         <v>2039</v>
       </c>
-      <c r="R98" t="s">
+      <c r="T98" t="s">
         <v>2040</v>
       </c>
-      <c r="S98" t="s">
+      <c r="U98" t="s">
         <v>2041</v>
       </c>
-      <c r="T98" t="s">
+      <c r="V98" t="s">
         <v>2042</v>
-      </c>
-      <c r="U98" t="s">
-        <v>2043</v>
-      </c>
-      <c r="V98" t="s">
-        <v>2044</v>
       </c>
     </row>
   </sheetData>
@@ -13377,57 +13381,56 @@
     <hyperlink ref="D45" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
     <hyperlink ref="D46" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
     <hyperlink ref="D47" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="D48" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="D49" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="D50" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="D51" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="D52" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="D53" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="D54" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="D55" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="D58" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="D59" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="D61" r:id="rId57" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="D62" r:id="rId58" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="D63" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="D64" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="D65" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="D66" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="D67" r:id="rId63" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="D68" r:id="rId64" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="D69" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="D70" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="D71" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="D72" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="D73" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="D74" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="D75" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="D76" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="D77" r:id="rId73" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="D78" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="D79" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="D80" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="D81" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="D82" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="D83" r:id="rId79" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="D84" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="D85" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="D86" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="D87" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="D88" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="D89" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="D90" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="D91" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="D92" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="D93" r:id="rId89" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="D94" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="D95" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="D96" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="D97" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="D98" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="D49" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="D50" r:id="rId48" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="D51" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="D52" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="D53" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="D54" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="D55" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="D58" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="D59" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="D61" r:id="rId56" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="D62" r:id="rId57" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="D63" r:id="rId58" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="D64" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="D65" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="D66" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="D67" r:id="rId62" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="D68" r:id="rId63" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="D69" r:id="rId64" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="D70" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="D71" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="D72" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="D73" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="D74" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="D75" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="D76" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="D77" r:id="rId72" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="D78" r:id="rId73" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="D79" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="D80" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="D81" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="D82" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="D83" r:id="rId78" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="D84" r:id="rId79" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="D85" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="D86" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="D87" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="D88" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="D89" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="D90" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="D91" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="D92" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="D93" r:id="rId88" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="D94" r:id="rId89" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="D95" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="D96" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="D97" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="D98" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="200" verticalDpi="200"/>
+  <pageSetup orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId94"/>
   <legacyDrawing r:id="rId95"/>
 </worksheet>
 </file>